--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB492C66-638D-467D-9859-4EFA5EDE96BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7949F2-4E4F-4414-AA46-29B10B477703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -484,7 +484,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -649,17 +649,17 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -667,14 +667,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1068,18 +1065,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
   <dimension ref="A1:O305"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1123,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="67"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1171,7 +1168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1265,7 +1262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1312,7 +1309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1359,7 +1356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1406,7 +1403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1453,7 +1450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1500,7 +1497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1547,7 +1544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1594,7 +1591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1641,7 +1638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="66" t="s">
         <v>0</v>
       </c>
@@ -1667,7 +1664,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="67"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1691,7 +1688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1717,7 +1714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1743,7 +1740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1769,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1795,7 +1792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1821,7 +1818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1847,7 +1844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1873,7 +1870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1899,7 +1896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1925,7 +1922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1951,7 +1948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="66" t="s">
         <v>0</v>
       </c>
@@ -1977,7 +1974,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="67"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -2001,7 +1998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2027,7 +2024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2053,7 +2050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2079,7 +2076,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2105,7 +2102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2131,7 +2128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2157,7 +2154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2183,7 +2180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2209,7 +2206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2235,7 +2232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2261,8 +2258,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="65" t="s">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2287,8 +2284,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="65"/>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="64"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2311,7 +2308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2337,7 +2334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2363,7 +2360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2389,7 +2386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2415,7 +2412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2441,7 +2438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2467,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2493,7 +2490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2519,7 +2516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2545,7 +2542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2571,8 +2568,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6">
-      <c r="A53" s="65" t="s">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2597,8 +2594,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6">
-      <c r="A54" s="65"/>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="64"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2647,7 +2644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2673,7 +2670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2699,7 +2696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2725,7 +2722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2751,7 +2748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2777,7 +2774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2803,7 +2800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2829,7 +2826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2855,7 +2852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2881,8 +2878,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6">
-      <c r="A66" s="65" t="s">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2907,8 +2904,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6">
-      <c r="A67" s="65"/>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="64"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2931,7 +2928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2957,7 +2954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2983,7 +2980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -3009,7 +3006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3035,7 +3032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3061,7 +3058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3087,7 +3084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3113,7 +3110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3139,7 +3136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3165,7 +3162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3191,8 +3188,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6">
-      <c r="A79" s="65" t="s">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3217,8 +3214,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6">
-      <c r="A80" s="65"/>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="64"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3241,7 +3238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3267,7 +3264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3293,7 +3290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3319,7 +3316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3338,10 +3335,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="69"/>
-      <c r="H84" s="70"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6">
+      <c r="G84" s="62"/>
+      <c r="H84" s="63"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3367,7 +3364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3393,7 +3390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3419,7 +3416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3445,7 +3442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3471,7 +3468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3497,8 +3494,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6">
-      <c r="A92" s="65" t="s">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3523,8 +3520,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6">
-      <c r="A93" s="65"/>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="64"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3547,7 +3544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3573,7 +3570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3599,7 +3596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3625,7 +3622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3651,7 +3648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3677,7 +3674,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3703,7 +3700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3729,7 +3726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3755,7 +3752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3781,8 +3778,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6">
-      <c r="A104" s="65" t="s">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3807,8 +3804,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6">
-      <c r="A105" s="65"/>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="64"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3831,7 +3828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3857,7 +3854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3883,7 +3880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3909,7 +3906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3935,7 +3932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3961,7 +3958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3987,7 +3984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -4013,7 +4010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4039,7 +4036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4065,8 +4062,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6">
-      <c r="A116" s="65" t="s">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4091,8 +4088,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6">
-      <c r="A117" s="65"/>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="64"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4115,7 +4112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4141,7 +4138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4167,7 +4164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4193,7 +4190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4219,7 +4216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4245,7 +4242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4271,7 +4268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4297,7 +4294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4323,7 +4320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4349,7 +4346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4375,7 +4372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4401,7 +4398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4427,7 +4424,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4451,7 +4448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4477,7 +4474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4503,7 +4500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4529,7 +4526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4555,7 +4552,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4581,7 +4578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4607,7 +4604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4633,7 +4630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4659,7 +4656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4685,7 +4682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4711,7 +4708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4737,7 +4734,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4763,8 +4760,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6">
-      <c r="A145" s="65" t="s">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4789,8 +4786,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6">
-      <c r="A146" s="65"/>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="64"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4813,7 +4810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4839,7 +4836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4865,7 +4862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4891,7 +4888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4917,7 +4914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4943,7 +4940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4969,7 +4966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4995,7 +4992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5021,7 +5018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5047,7 +5044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5073,7 +5070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5099,7 +5096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5125,8 +5122,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6">
-      <c r="A160" s="65" t="s">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5151,8 +5148,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6">
-      <c r="A161" s="65"/>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="64"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5175,7 +5172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5201,7 +5198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5227,7 +5224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5253,7 +5250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5279,7 +5276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5305,7 +5302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5331,7 +5328,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5357,7 +5354,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5383,7 +5380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5409,7 +5406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5435,7 +5432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5461,7 +5458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5487,8 +5484,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6">
-      <c r="A175" s="65" t="s">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5513,8 +5510,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6">
-      <c r="A176" s="65"/>
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="64"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5537,7 +5534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5563,7 +5560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5589,7 +5586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5615,7 +5612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5641,7 +5638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5667,7 +5664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5693,7 +5690,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5719,7 +5716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5745,7 +5742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5771,7 +5768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5797,7 +5794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5823,7 +5820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5849,8 +5846,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.6">
-      <c r="A190" s="65" t="s">
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5875,8 +5872,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.6">
-      <c r="A191" s="65"/>
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="64"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5899,7 +5896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.6">
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5925,7 +5922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.6">
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5951,7 +5948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.6">
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5977,7 +5974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.6">
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -6003,7 +6000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.6">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6029,7 +6026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.6">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6055,7 +6052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.6">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6081,7 +6078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.6">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6107,7 +6104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.6">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6133,7 +6130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.6">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6159,7 +6156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.6">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6185,7 +6182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.6">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6211,8 +6208,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="63" t="s">
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6237,8 +6234,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="63"/>
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="65"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6261,7 +6258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.6">
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6287,7 +6284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.6">
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6313,7 +6310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.8">
+    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6339,7 +6336,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.6">
+    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6365,7 +6362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="31.2">
+    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6391,7 +6388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="31.2">
+    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6417,7 +6414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.6">
+    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6443,7 +6440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.6">
+    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6469,7 +6466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.6">
+    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6495,7 +6492,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.6">
+    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6521,7 +6518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.6">
+    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6547,7 +6544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.6">
+    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6573,7 +6570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6583,8 +6580,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="63" t="s">
+    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6609,8 +6606,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="63"/>
+    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="65"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6633,7 +6630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.6">
+    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6659,7 +6656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.6">
+    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6685,7 +6682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.6">
+    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6711,7 +6708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.6">
+    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6737,7 +6734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="31.2">
+    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6763,7 +6760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.6">
+    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6789,7 +6786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.6">
+    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6815,7 +6812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.6">
+    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6841,7 +6838,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.6">
+    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6867,7 +6864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.6">
+    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6893,7 +6890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.6">
+    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6919,7 +6916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.6">
+    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6945,8 +6942,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="63" t="s">
+    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6971,8 +6968,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="63"/>
+    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="65"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -6995,7 +6992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.6">
+    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7021,7 +7018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.6">
+    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7047,7 +7044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.6">
+    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7073,7 +7070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="31.2">
+    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7099,7 +7096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.6">
+    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7125,7 +7122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.6">
+    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7151,7 +7148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.6">
+    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7177,7 +7174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.6">
+    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7203,7 +7200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.6">
+    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7229,7 +7226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.6">
+    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7255,7 +7252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.6">
+    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7281,7 +7278,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.6">
+    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7307,8 +7304,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="63" t="s">
+    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7333,8 +7330,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="63"/>
+    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="65"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7357,7 +7354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.6">
+    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7383,7 +7380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.6">
+    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7409,7 +7406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.6">
+    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7435,7 +7432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.6">
+    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7461,7 +7458,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.6">
+    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7487,7 +7484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.6">
+    <row r="257" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7513,7 +7510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.6">
+    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7539,7 +7536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.6">
+    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7565,7 +7562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.6">
+    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7591,7 +7588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.6">
+    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7617,7 +7614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.6">
+    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7643,7 +7640,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.6">
+    <row r="263" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7669,8 +7666,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="63" t="s">
+    <row r="265" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A265" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7695,8 +7692,8 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="64"/>
+    <row r="266" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A266" s="68"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7719,7 +7716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.6">
+    <row r="267" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7745,7 +7742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.6">
+    <row r="268" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7771,7 +7768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.6">
+    <row r="269" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7797,7 +7794,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.6">
+    <row r="270" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7823,7 +7820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="31.2">
+    <row r="271" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -7849,7 +7846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.6">
+    <row r="272" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -7875,7 +7872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.6">
+    <row r="273" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -7901,7 +7898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.6">
+    <row r="274" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -7927,7 +7924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.6">
+    <row r="275" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -7953,7 +7950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.6">
+    <row r="276" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -7979,7 +7976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.6">
+    <row r="277" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -8005,8 +8002,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="68" t="s">
+    <row r="279" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A279" s="69" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8031,8 +8028,8 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="68"/>
+    <row r="280" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A280" s="69"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8055,7 +8052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.6">
+    <row r="281" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8081,7 +8078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.6">
+    <row r="282" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8107,7 +8104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="31.2">
+    <row r="283" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8133,7 +8130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.6">
+    <row r="284" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8159,7 +8156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.6">
+    <row r="285" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8185,7 +8182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.6">
+    <row r="286" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8211,7 +8208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.6">
+    <row r="287" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8237,7 +8234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.6">
+    <row r="288" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8263,7 +8260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.6">
+    <row r="289" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8289,7 +8286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.6">
+    <row r="290" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8315,7 +8312,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.6">
+    <row r="291" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8341,8 +8338,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="63" t="s">
+    <row r="293" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A293" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8367,8 +8364,8 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="64"/>
+    <row r="294" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A294" s="68"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8391,7 +8388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="15.6">
+    <row r="295" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
@@ -8417,7 +8414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="31.2">
+    <row r="296" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
@@ -8443,7 +8440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="31.2">
+    <row r="297" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
@@ -8469,7 +8466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="15.6">
+    <row r="298" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
@@ -8495,7 +8492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="15.6">
+    <row r="299" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
@@ -8521,7 +8518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="15.6">
+    <row r="300" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
@@ -8547,7 +8544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="15.6">
+    <row r="301" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
@@ -8573,7 +8570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="15.6">
+    <row r="302" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
@@ -8599,7 +8596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15.6">
+    <row r="303" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
@@ -8625,7 +8622,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="15.6">
+    <row r="304" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
@@ -8651,7 +8648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="15.6">
+    <row r="305" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
@@ -8673,12 +8670,25 @@
       <c r="G305" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H305" s="62" t="s">
-        <v>34</v>
+      <c r="H305" s="29" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A293:A294"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A279:A280"/>
+    <mergeCell ref="A265:A266"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
@@ -8688,19 +8698,6 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A293:A294"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A279:A280"/>
-    <mergeCell ref="A265:A266"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8709,26 +8706,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -8929,10 +8906,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8949,20 +8957,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7949F2-4E4F-4414-AA46-29B10B477703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7530588-D762-4901-B952-D177C78B279F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +308,23 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="14">
@@ -484,7 +501,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -649,16 +666,16 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -667,10 +684,43 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1064,19 +1114,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O305"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O319"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6">
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
@@ -1123,7 +1173,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.6">
       <c r="A2" s="67"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1168,7 +1218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.75">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1215,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.75">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1262,7 +1312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.75">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1356,7 +1406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.75">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1403,7 +1453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1450,7 +1500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.75">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1497,7 +1547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.75">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1544,7 +1594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.75">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1591,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.75">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1638,7 +1688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.6">
       <c r="A14" s="66" t="s">
         <v>0</v>
       </c>
@@ -1664,7 +1714,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15.6">
       <c r="A15" s="67"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1688,7 +1738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.75">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1714,7 +1764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1766,7 +1816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1792,7 +1842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1818,7 +1868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.75">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1844,7 +1894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.75">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1870,7 +1920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.75">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1896,7 +1946,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.75">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1922,7 +1972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.75">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1948,7 +1998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.6">
       <c r="A27" s="66" t="s">
         <v>0</v>
       </c>
@@ -1974,7 +2024,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.6">
       <c r="A28" s="67"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -1998,7 +2048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.75">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2024,7 +2074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.75">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2050,7 +2100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.75">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2076,7 +2126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.75">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2102,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.75">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2128,7 +2178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.75">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2154,7 +2204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.75">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2180,7 +2230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.75">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2206,7 +2256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.75">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2232,7 +2282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.75">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2258,7 +2308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="15.6">
       <c r="A40" s="64" t="s">
         <v>0</v>
       </c>
@@ -2284,7 +2334,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="15.6">
       <c r="A41" s="64"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -2308,7 +2358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.75">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2334,7 +2384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.75">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2360,7 +2410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.75">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2386,7 +2436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.75">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2412,7 +2462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.75">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2438,7 +2488,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.75">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2464,7 +2514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.75">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2490,7 +2540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.75">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2516,7 +2566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.75">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2542,7 +2592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.75">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="15.6">
       <c r="A53" s="64" t="s">
         <v>0</v>
       </c>
@@ -2594,7 +2644,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15.6">
       <c r="A54" s="64"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2618,7 +2668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.75">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2644,7 +2694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.75">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2670,7 +2720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.75">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2696,7 +2746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.75">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2722,7 +2772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.75">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2748,7 +2798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.75">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2774,7 +2824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.75">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2800,7 +2850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.75">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2826,7 +2876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.75">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2852,7 +2902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.75">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2878,7 +2928,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15.6">
       <c r="A66" s="64" t="s">
         <v>0</v>
       </c>
@@ -2904,7 +2954,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="15.6">
       <c r="A67" s="64"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -2928,7 +2978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.75">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2954,7 +3004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.75">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2980,7 +3030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.75">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -3006,7 +3056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.75">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3032,7 +3082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.75">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3058,7 +3108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.75">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3084,7 +3134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.75">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3110,7 +3160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.75">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3136,7 +3186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.75">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3162,7 +3212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.75">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3188,7 +3238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15.6">
       <c r="A79" s="64" t="s">
         <v>0</v>
       </c>
@@ -3214,7 +3264,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="15.6">
       <c r="A80" s="64"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -3238,7 +3288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.75">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3264,7 +3314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.75">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3290,7 +3340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.75">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3316,7 +3366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.75">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3335,10 +3385,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="62"/>
-      <c r="H84" s="63"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G84" s="68"/>
+      <c r="H84" s="69"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3364,7 +3414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.75">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3390,7 +3440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.75">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3416,7 +3466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.75">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3442,7 +3492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.75">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3468,7 +3518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.75">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3494,7 +3544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="15.6">
       <c r="A92" s="64" t="s">
         <v>0</v>
       </c>
@@ -3520,7 +3570,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="15.6">
       <c r="A93" s="64"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
@@ -3544,7 +3594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.75">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3570,7 +3620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.75">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3596,7 +3646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.75">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3622,7 +3672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.75">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3648,7 +3698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.75">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3674,7 +3724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.75">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3700,7 +3750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.75">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3726,7 +3776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.75">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3752,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.75">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3778,7 +3828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="15.6">
       <c r="A104" s="64" t="s">
         <v>0</v>
       </c>
@@ -3804,7 +3854,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="15.6">
       <c r="A105" s="64"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
@@ -3828,7 +3878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.75">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3854,7 +3904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.75">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3880,7 +3930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.75">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3906,7 +3956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.75">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3932,7 +3982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.75">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3958,7 +4008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.75">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3984,7 +4034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.75">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -4010,7 +4060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.75">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4036,7 +4086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.75">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4062,7 +4112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="15.6">
       <c r="A116" s="64" t="s">
         <v>0</v>
       </c>
@@ -4088,7 +4138,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ht="15.6">
       <c r="A117" s="64"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
@@ -4112,7 +4162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.75">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4138,7 +4188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.75">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4164,7 +4214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.75">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4190,7 +4240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.75">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4216,7 +4266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.75">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4242,7 +4292,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.75">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4268,7 +4318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.75">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4294,7 +4344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.75">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4320,7 +4370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.75">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4346,7 +4396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.75">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4372,7 +4422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.75">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4398,7 +4448,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.75">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4424,7 +4474,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.6">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4448,7 +4498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.75">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4474,7 +4524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.75">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4500,7 +4550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.75">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4526,7 +4576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.75">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4552,7 +4602,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.75">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4578,7 +4628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.75">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4604,7 +4654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.75">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4630,7 +4680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.75">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4656,7 +4706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.75">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4682,7 +4732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.75">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4708,7 +4758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.75">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4734,7 +4784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.75">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4760,7 +4810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="15.6">
       <c r="A145" s="64" t="s">
         <v>0</v>
       </c>
@@ -4786,7 +4836,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="15.6">
       <c r="A146" s="64"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
@@ -4810,7 +4860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.75">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4836,7 +4886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.75">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4862,7 +4912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.75">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4888,7 +4938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.75">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4914,7 +4964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.75">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4940,7 +4990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.75">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4966,7 +5016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.75">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4992,7 +5042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.75">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5018,7 +5068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.75">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5044,7 +5094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.75">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5070,7 +5120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.75">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5096,7 +5146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.75">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5122,7 +5172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="15.6">
       <c r="A160" s="64" t="s">
         <v>0</v>
       </c>
@@ -5148,7 +5198,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="15.6">
       <c r="A161" s="64"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
@@ -5172,7 +5222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.75">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5198,7 +5248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.75">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5224,7 +5274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.75">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5250,7 +5300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.75">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5276,7 +5326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.75">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5302,7 +5352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.75">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5328,7 +5378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.75">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5354,7 +5404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.75">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5380,7 +5430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.75">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5406,7 +5456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.75">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5432,7 +5482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.75">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5458,7 +5508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.75">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5484,7 +5534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="15.6">
       <c r="A175" s="64" t="s">
         <v>0</v>
       </c>
@@ -5510,7 +5560,7 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="15.6">
       <c r="A176" s="64"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
@@ -5534,7 +5584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="15.75">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5560,7 +5610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="15.75">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5586,7 +5636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="15.75">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5612,7 +5662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="15.75">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5638,7 +5688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="15.75">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5664,7 +5714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="15.75">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5690,7 +5740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15.75">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5716,7 +5766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="15.75">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5742,7 +5792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="15.75">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5768,7 +5818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="15.75">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5794,7 +5844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="15.75">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5820,7 +5870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="15.75">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5846,7 +5896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" ht="15.6">
       <c r="A190" s="64" t="s">
         <v>0</v>
       </c>
@@ -5872,7 +5922,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" ht="15.6">
       <c r="A191" s="64"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
@@ -5896,7 +5946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="15.75">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5922,7 +5972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="15.75">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5948,7 +5998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="15.75">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5974,7 +6024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="15.75">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -6000,7 +6050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="15.75">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6026,7 +6076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="15.6">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6052,7 +6102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="15.75">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6078,7 +6128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="15.6">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6104,7 +6154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="15.75">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6130,7 +6180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="15.75">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6156,7 +6206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="15.75">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6182,7 +6232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="15.75">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6208,8 +6258,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="65" t="s">
+    <row r="205" spans="1:8" ht="15.6">
+      <c r="A205" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6234,8 +6284,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="65"/>
+    <row r="206" spans="1:8" ht="15.6">
+      <c r="A206" s="62"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6258,7 +6308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="15.75">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6284,7 +6334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="15.75">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6310,7 +6360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="46.8">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6336,7 +6386,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="15.75">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6362,7 +6412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="47.25">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6388,7 +6438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="31.2">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6414,7 +6464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="15.75">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6440,7 +6490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="15.75">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6466,7 +6516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="15.75">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6492,7 +6542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="15.75">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6518,7 +6568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.75">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6544,7 +6594,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="15.6">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6570,7 +6620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="15">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6580,8 +6630,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="65" t="s">
+    <row r="220" spans="1:8" ht="15.6">
+      <c r="A220" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6606,8 +6656,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="65"/>
+    <row r="221" spans="1:8" ht="15.6">
+      <c r="A221" s="62"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6630,7 +6680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="15.6">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6656,7 +6706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="15.75">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6682,7 +6732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="15.75">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6708,7 +6758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" ht="15.75">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6734,7 +6784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="47.25">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6760,7 +6810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="15.75">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6786,7 +6836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="15.75">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6812,7 +6862,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" ht="15.6">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6838,7 +6888,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="15.75">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6864,7 +6914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="15.75">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6890,7 +6940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" ht="15.6">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6916,7 +6966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="15.75">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6942,8 +6992,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="65" t="s">
+    <row r="235" spans="1:8" ht="15.6">
+      <c r="A235" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6968,8 +7018,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="65"/>
+    <row r="236" spans="1:8" ht="15.6">
+      <c r="A236" s="62"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -6992,7 +7042,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" ht="15.75">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7018,7 +7068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" ht="15.75">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7044,7 +7094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" ht="15.75">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7070,7 +7120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="47.25">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7096,7 +7146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" ht="15.75">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7122,7 +7172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" ht="15.75">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7148,7 +7198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" ht="15.75">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7174,7 +7224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" ht="15.75">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7200,7 +7250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" ht="15.75">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7226,7 +7276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" ht="15.75">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7252,7 +7302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" ht="15.75">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7278,7 +7328,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" ht="15.75">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7304,8 +7354,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="65" t="s">
+    <row r="250" spans="1:8" ht="15.6">
+      <c r="A250" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7330,8 +7380,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="65"/>
+    <row r="251" spans="1:8" ht="15.6">
+      <c r="A251" s="62"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7354,7 +7404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" ht="15.75">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7380,7 +7430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" ht="15.75">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7406,7 +7456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" ht="15.75">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7432,7 +7482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" ht="15.75">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7458,7 +7508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" ht="15.75">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7484,7 +7534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" ht="15.75">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7510,7 +7560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" ht="15.75">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7536,7 +7586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" ht="15.75">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7562,7 +7612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" ht="15.75">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7588,7 +7638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="15.75">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7614,7 +7664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" ht="15.75">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7640,7 +7690,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" ht="15.75">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7666,8 +7716,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A265" s="65" t="s">
+    <row r="265" spans="1:8" ht="15.6">
+      <c r="A265" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7692,8 +7742,8 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A266" s="68"/>
+    <row r="266" spans="1:8" ht="15.6">
+      <c r="A266" s="63"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7716,7 +7766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" ht="15.75">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7742,7 +7792,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" ht="15.75">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7768,7 +7818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" ht="15.75">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7794,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" ht="15.75">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7820,7 +7870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" ht="47.25">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -7846,7 +7896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" ht="15.75">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -7872,7 +7922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" ht="15.75">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -7898,7 +7948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" ht="15.75">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -7924,7 +7974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" ht="15.75">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -7950,7 +8000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" ht="15.75">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -7976,7 +8026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" ht="15.75">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -8002,8 +8052,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A279" s="69" t="s">
+    <row r="279" spans="1:8" ht="15.6">
+      <c r="A279" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8028,8 +8078,8 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="69"/>
+    <row r="280" spans="1:8" ht="15.6">
+      <c r="A280" s="65"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8052,7 +8102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" ht="15.75">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8078,7 +8128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" ht="15.75">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8104,7 +8154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" ht="47.25">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8130,7 +8180,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" ht="15.75">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8156,7 +8206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" ht="15.75">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8182,7 +8232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" ht="15.75">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8208,7 +8258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" ht="15.75">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8234,7 +8284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" ht="15.75">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8260,7 +8310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" ht="15.75">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8286,7 +8336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" ht="15.75">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8312,7 +8362,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" ht="15.75">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8338,8 +8388,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A293" s="65" t="s">
+    <row r="293" spans="1:8" ht="15.6">
+      <c r="A293" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8364,8 +8414,8 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A294" s="68"/>
+    <row r="294" spans="1:8" ht="15.6">
+      <c r="A294" s="63"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8388,7 +8438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" ht="15.75">
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
@@ -8414,7 +8464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" ht="47.25">
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
@@ -8440,7 +8490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" ht="31.5">
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
@@ -8466,7 +8516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" ht="15.75">
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
@@ -8492,7 +8542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" ht="15.75">
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
@@ -8518,7 +8568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" ht="15.75">
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
@@ -8544,7 +8594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" ht="15.75">
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
@@ -8570,7 +8620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" ht="15.75">
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
@@ -8596,7 +8646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" ht="15.75">
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
@@ -8622,7 +8672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" ht="15.75">
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
@@ -8648,7 +8698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" ht="15.75">
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
@@ -8674,21 +8724,345 @@
         <v>10</v>
       </c>
     </row>
+    <row r="307" spans="1:8" ht="15.6">
+      <c r="A307" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B307" s="70">
+        <v>46286</v>
+      </c>
+      <c r="C307" s="70">
+        <v>46287</v>
+      </c>
+      <c r="D307" s="70">
+        <v>46288</v>
+      </c>
+      <c r="E307" s="70">
+        <v>46289</v>
+      </c>
+      <c r="F307" s="70">
+        <v>46290</v>
+      </c>
+      <c r="G307" s="70">
+        <v>46291</v>
+      </c>
+      <c r="H307" s="70">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="15.6">
+      <c r="A308" s="80"/>
+      <c r="B308" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C308" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D308" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E308" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="F308" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="G308" s="71" t="s">
+        <v>6</v>
+      </c>
+      <c r="H308" s="71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" ht="31.2">
+      <c r="A309" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="B309" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C309" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="D309" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="E309" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="F309" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G309" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="H309" s="73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="15.6">
+      <c r="A310" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B310" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C310" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D310" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F310" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G310" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="H310" s="74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="15.6">
+      <c r="A311" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B311" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C311" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D311" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F311" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G311" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="H311" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="15.6">
+      <c r="A312" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B312" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C312" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D312" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F312" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G312" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="H312" s="74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" ht="15.6">
+      <c r="A313" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B313" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C313" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D313" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F313" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G313" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H313" s="76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" ht="15.6">
+      <c r="A314" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B314" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C314" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D314" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E314" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F314" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" s="73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" ht="15.6">
+      <c r="A315" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B315" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C315" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D315" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E315" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F315" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" s="73" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" ht="15.6">
+      <c r="A316" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="B316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G316" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H316" s="74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="15.6">
+      <c r="A317" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B317" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D317" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E317" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F317" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G317" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="H317" s="74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" ht="15.6">
+      <c r="A318" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="B318" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C318" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D318" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E318" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F318" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G318" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H318" s="76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" ht="15.6">
+      <c r="A319" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B319" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C319" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D319" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E319" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F319" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G319" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="H319" s="78" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A293:A294"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A279:A280"/>
-    <mergeCell ref="A265:A266"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="23">
+    <mergeCell ref="A307:A308"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
@@ -8698,6 +9072,19 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A293:A294"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A279:A280"/>
+    <mergeCell ref="A265:A266"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8706,6 +9093,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -8906,17 +9304,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8927,6 +9314,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8945,17 +9343,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7530588-D762-4901-B952-D177C78B279F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2142ED8-0258-412C-852C-3A508DF4CFD9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -501,7 +501,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,38 +666,11 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -711,17 +684,41 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1127,7 +1124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1174,7 +1171,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="67"/>
+      <c r="A2" s="74"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75">
+    <row r="3" spans="1:15" ht="15.6">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1265,7 +1262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75">
+    <row r="4" spans="1:15" ht="15.6">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1312,7 +1309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75">
+    <row r="5" spans="1:15" ht="15.6">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1406,7 +1403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75">
+    <row r="7" spans="1:15" ht="15.6">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1453,7 +1450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75">
+    <row r="8" spans="1:15" ht="15.6">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1500,7 +1497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75">
+    <row r="9" spans="1:15" ht="15.6">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1547,7 +1544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75">
+    <row r="10" spans="1:15" ht="15.6">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1594,7 +1591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75">
+    <row r="11" spans="1:15" ht="15.6">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1641,7 +1638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75">
+    <row r="12" spans="1:15" ht="15.6">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1689,7 +1686,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1715,7 +1712,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6">
-      <c r="A15" s="67"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1738,7 +1735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75">
+    <row r="16" spans="1:15" ht="15.6">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1764,7 +1761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75">
+    <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1790,7 +1787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75">
+    <row r="18" spans="1:8" ht="15.6">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1816,7 +1813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75">
+    <row r="19" spans="1:8" ht="15.6">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1842,7 +1839,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75">
+    <row r="20" spans="1:8" ht="15.6">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1868,7 +1865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75">
+    <row r="21" spans="1:8" ht="15.6">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1894,7 +1891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75">
+    <row r="22" spans="1:8" ht="15.6">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1920,7 +1917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75">
+    <row r="23" spans="1:8" ht="15.6">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1946,7 +1943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75">
+    <row r="24" spans="1:8" ht="15.6">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1972,7 +1969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75">
+    <row r="25" spans="1:8" ht="15.6">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1999,7 +1996,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2025,7 +2022,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6">
-      <c r="A28" s="67"/>
+      <c r="A28" s="74"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2048,7 +2045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75">
+    <row r="29" spans="1:8" ht="15.6">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2074,7 +2071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75">
+    <row r="30" spans="1:8" ht="15.6">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2100,7 +2097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75">
+    <row r="31" spans="1:8" ht="15.6">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2126,7 +2123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75">
+    <row r="32" spans="1:8" ht="15.6">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2152,7 +2149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75">
+    <row r="33" spans="1:8" ht="15.6">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2178,7 +2175,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75">
+    <row r="34" spans="1:8" ht="15.6">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2204,7 +2201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75">
+    <row r="35" spans="1:8" ht="15.6">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2230,7 +2227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75">
+    <row r="36" spans="1:8" ht="15.6">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2256,7 +2253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75">
+    <row r="37" spans="1:8" ht="15.6">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2282,7 +2279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75">
+    <row r="38" spans="1:8" ht="15.6">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2309,7 +2306,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2335,7 +2332,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="64"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2358,7 +2355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75">
+    <row r="42" spans="1:8" ht="15.6">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2384,7 +2381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75">
+    <row r="43" spans="1:8" ht="15.6">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2410,7 +2407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75">
+    <row r="44" spans="1:8" ht="15.6">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2436,7 +2433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75">
+    <row r="45" spans="1:8" ht="15.6">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2462,7 +2459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75">
+    <row r="46" spans="1:8" ht="15.6">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2488,7 +2485,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75">
+    <row r="47" spans="1:8" ht="15.6">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2514,7 +2511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75">
+    <row r="48" spans="1:8" ht="15.6">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2540,7 +2537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75">
+    <row r="49" spans="1:8" ht="15.6">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2566,7 +2563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75">
+    <row r="50" spans="1:8" ht="15.6">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2592,7 +2589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75">
+    <row r="51" spans="1:8" ht="15.6">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2619,7 +2616,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6">
-      <c r="A53" s="64" t="s">
+      <c r="A53" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2645,7 +2642,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6">
-      <c r="A54" s="64"/>
+      <c r="A54" s="71"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2668,7 +2665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75">
+    <row r="55" spans="1:8" ht="15.6">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2694,7 +2691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75">
+    <row r="56" spans="1:8" ht="15.6">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2720,7 +2717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75">
+    <row r="57" spans="1:8" ht="15.6">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2746,7 +2743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75">
+    <row r="58" spans="1:8" ht="15.6">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2772,7 +2769,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75">
+    <row r="59" spans="1:8" ht="15.6">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2798,7 +2795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75">
+    <row r="60" spans="1:8" ht="15.6">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2824,7 +2821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75">
+    <row r="61" spans="1:8" ht="15.6">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2850,7 +2847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75">
+    <row r="62" spans="1:8" ht="15.6">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2876,7 +2873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75">
+    <row r="63" spans="1:8" ht="15.6">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2902,7 +2899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75">
+    <row r="64" spans="1:8" ht="15.6">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2929,7 +2926,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2955,7 +2952,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6">
-      <c r="A67" s="64"/>
+      <c r="A67" s="71"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2978,7 +2975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75">
+    <row r="68" spans="1:8" ht="15.6">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -3004,7 +3001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75">
+    <row r="69" spans="1:8" ht="15.6">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -3030,7 +3027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75">
+    <row r="70" spans="1:8" ht="15.6">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -3056,7 +3053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75">
+    <row r="71" spans="1:8" ht="15.6">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3082,7 +3079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75">
+    <row r="72" spans="1:8" ht="15.6">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3108,7 +3105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75">
+    <row r="73" spans="1:8" ht="15.6">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3134,7 +3131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75">
+    <row r="74" spans="1:8" ht="15.6">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3160,7 +3157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75">
+    <row r="75" spans="1:8" ht="15.6">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3186,7 +3183,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75">
+    <row r="76" spans="1:8" ht="15.6">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3212,7 +3209,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75">
+    <row r="77" spans="1:8" ht="15.6">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3239,7 +3236,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6">
-      <c r="A79" s="64" t="s">
+      <c r="A79" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3265,7 +3262,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6">
-      <c r="A80" s="64"/>
+      <c r="A80" s="71"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3288,7 +3285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75">
+    <row r="81" spans="1:8" ht="15.6">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3314,7 +3311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75">
+    <row r="82" spans="1:8" ht="15.6">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3340,7 +3337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75">
+    <row r="83" spans="1:8" ht="15.6">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3366,7 +3363,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75">
+    <row r="84" spans="1:8" ht="15.6">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3385,10 +3382,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="68"/>
-      <c r="H84" s="69"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75">
+      <c r="G84" s="69"/>
+      <c r="H84" s="70"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.6">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3414,7 +3411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75">
+    <row r="86" spans="1:8" ht="15.6">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3440,7 +3437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75">
+    <row r="87" spans="1:8" ht="15.6">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3466,7 +3463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75">
+    <row r="88" spans="1:8" ht="15.6">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3492,7 +3489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75">
+    <row r="89" spans="1:8" ht="15.6">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3518,7 +3515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75">
+    <row r="90" spans="1:8" ht="15.6">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3545,7 +3542,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6">
-      <c r="A92" s="64" t="s">
+      <c r="A92" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3571,7 +3568,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6">
-      <c r="A93" s="64"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3594,7 +3591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75">
+    <row r="94" spans="1:8" ht="15.6">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3620,7 +3617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75">
+    <row r="95" spans="1:8" ht="15.6">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3646,7 +3643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75">
+    <row r="96" spans="1:8" ht="15.6">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3672,7 +3669,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75">
+    <row r="97" spans="1:8" ht="15.6">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3698,7 +3695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75">
+    <row r="98" spans="1:8" ht="15.6">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3724,7 +3721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75">
+    <row r="99" spans="1:8" ht="15.6">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3750,7 +3747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75">
+    <row r="100" spans="1:8" ht="15.6">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3776,7 +3773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75">
+    <row r="101" spans="1:8" ht="15.6">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3802,7 +3799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75">
+    <row r="102" spans="1:8" ht="15.6">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3829,7 +3826,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6">
-      <c r="A104" s="64" t="s">
+      <c r="A104" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3855,7 +3852,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6">
-      <c r="A105" s="64"/>
+      <c r="A105" s="71"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3878,7 +3875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75">
+    <row r="106" spans="1:8" ht="15.6">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3904,7 +3901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75">
+    <row r="107" spans="1:8" ht="15.6">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3930,7 +3927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75">
+    <row r="108" spans="1:8" ht="15.6">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3956,7 +3953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75">
+    <row r="109" spans="1:8" ht="15.6">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3982,7 +3979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75">
+    <row r="110" spans="1:8" ht="15.6">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -4008,7 +4005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75">
+    <row r="111" spans="1:8" ht="15.6">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -4034,7 +4031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75">
+    <row r="112" spans="1:8" ht="15.6">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -4060,7 +4057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75">
+    <row r="113" spans="1:8" ht="15.6">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4086,7 +4083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75">
+    <row r="114" spans="1:8" ht="15.6">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4113,7 +4110,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6">
-      <c r="A116" s="64" t="s">
+      <c r="A116" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4139,7 +4136,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6">
-      <c r="A117" s="64"/>
+      <c r="A117" s="71"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4162,7 +4159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75">
+    <row r="118" spans="1:8" ht="15.6">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4188,7 +4185,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75">
+    <row r="119" spans="1:8" ht="15.6">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4214,7 +4211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75">
+    <row r="120" spans="1:8" ht="15.6">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4240,7 +4237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75">
+    <row r="121" spans="1:8" ht="15.6">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4266,7 +4263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75">
+    <row r="122" spans="1:8" ht="15.6">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4292,7 +4289,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75">
+    <row r="123" spans="1:8" ht="15.6">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4318,7 +4315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75">
+    <row r="124" spans="1:8" ht="15.6">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4344,7 +4341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75">
+    <row r="125" spans="1:8" ht="15.6">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4370,7 +4367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75">
+    <row r="126" spans="1:8" ht="15.6">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4396,7 +4393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75">
+    <row r="127" spans="1:8" ht="15.6">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4422,7 +4419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75">
+    <row r="128" spans="1:8" ht="15.6">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4448,7 +4445,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75">
+    <row r="130" spans="1:8" ht="15.6">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4498,7 +4495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75">
+    <row r="132" spans="1:8" ht="15.6">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4524,7 +4521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75">
+    <row r="133" spans="1:8" ht="15.6">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4550,7 +4547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75">
+    <row r="134" spans="1:8" ht="15.6">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4576,7 +4573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75">
+    <row r="135" spans="1:8" ht="15.6">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4602,7 +4599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75">
+    <row r="136" spans="1:8" ht="15.6">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4628,7 +4625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75">
+    <row r="137" spans="1:8" ht="15.6">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4654,7 +4651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75">
+    <row r="138" spans="1:8" ht="15.6">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4680,7 +4677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75">
+    <row r="139" spans="1:8" ht="15.6">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4706,7 +4703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75">
+    <row r="140" spans="1:8" ht="15.6">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4732,7 +4729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75">
+    <row r="141" spans="1:8" ht="15.6">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4758,7 +4755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75">
+    <row r="142" spans="1:8" ht="15.6">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4784,7 +4781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75">
+    <row r="143" spans="1:8" ht="15.6">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4811,7 +4808,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6">
-      <c r="A145" s="64" t="s">
+      <c r="A145" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4837,7 +4834,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6">
-      <c r="A146" s="64"/>
+      <c r="A146" s="71"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4860,7 +4857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75">
+    <row r="147" spans="1:8" ht="15.6">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4886,7 +4883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75">
+    <row r="148" spans="1:8" ht="15.6">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4912,7 +4909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75">
+    <row r="149" spans="1:8" ht="15.6">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4938,7 +4935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75">
+    <row r="150" spans="1:8" ht="15.6">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4964,7 +4961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75">
+    <row r="151" spans="1:8" ht="15.6">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4990,7 +4987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75">
+    <row r="152" spans="1:8" ht="15.6">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -5016,7 +5013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75">
+    <row r="153" spans="1:8" ht="15.6">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -5042,7 +5039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75">
+    <row r="154" spans="1:8" ht="15.6">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5068,7 +5065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75">
+    <row r="155" spans="1:8" ht="15.6">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5094,7 +5091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75">
+    <row r="156" spans="1:8" ht="15.6">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5120,7 +5117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75">
+    <row r="157" spans="1:8" ht="15.6">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5146,7 +5143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75">
+    <row r="158" spans="1:8" ht="15.6">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5173,7 +5170,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6">
-      <c r="A160" s="64" t="s">
+      <c r="A160" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5199,7 +5196,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6">
-      <c r="A161" s="64"/>
+      <c r="A161" s="71"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5222,7 +5219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75">
+    <row r="162" spans="1:8" ht="15.6">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75">
+    <row r="163" spans="1:8" ht="15.6">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5274,7 +5271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75">
+    <row r="164" spans="1:8" ht="15.6">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5300,7 +5297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75">
+    <row r="165" spans="1:8" ht="15.6">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5326,7 +5323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75">
+    <row r="166" spans="1:8" ht="15.6">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5352,7 +5349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75">
+    <row r="167" spans="1:8" ht="15.6">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5378,7 +5375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75">
+    <row r="168" spans="1:8" ht="15.6">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5404,7 +5401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75">
+    <row r="169" spans="1:8" ht="15.6">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5430,7 +5427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75">
+    <row r="170" spans="1:8" ht="15.6">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5456,7 +5453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75">
+    <row r="171" spans="1:8" ht="15.6">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5482,7 +5479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75">
+    <row r="172" spans="1:8" ht="15.6">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5508,7 +5505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75">
+    <row r="173" spans="1:8" ht="15.6">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5535,7 +5532,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6">
-      <c r="A175" s="64" t="s">
+      <c r="A175" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5561,7 +5558,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6">
-      <c r="A176" s="64"/>
+      <c r="A176" s="71"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5584,7 +5581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75">
+    <row r="177" spans="1:8" ht="15.6">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5610,7 +5607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75">
+    <row r="178" spans="1:8" ht="15.6">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5636,7 +5633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75">
+    <row r="179" spans="1:8" ht="15.6">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5662,7 +5659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75">
+    <row r="180" spans="1:8" ht="15.6">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5688,7 +5685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75">
+    <row r="181" spans="1:8" ht="15.6">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5714,7 +5711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75">
+    <row r="182" spans="1:8" ht="15.6">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5740,7 +5737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75">
+    <row r="183" spans="1:8" ht="15.6">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5766,7 +5763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75">
+    <row r="184" spans="1:8" ht="15.6">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5792,7 +5789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75">
+    <row r="185" spans="1:8" ht="15.6">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5818,7 +5815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75">
+    <row r="186" spans="1:8" ht="15.6">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5844,7 +5841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75">
+    <row r="187" spans="1:8" ht="15.6">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5870,7 +5867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75">
+    <row r="188" spans="1:8" ht="15.6">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5897,7 +5894,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6">
-      <c r="A190" s="64" t="s">
+      <c r="A190" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5923,7 +5920,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6">
-      <c r="A191" s="64"/>
+      <c r="A191" s="71"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5946,7 +5943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75">
+    <row r="192" spans="1:8" ht="15.6">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5972,7 +5969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75">
+    <row r="193" spans="1:8" ht="15.6">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5998,7 +5995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75">
+    <row r="194" spans="1:8" ht="15.6">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -6024,7 +6021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75">
+    <row r="195" spans="1:8" ht="15.6">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -6050,7 +6047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75">
+    <row r="196" spans="1:8" ht="15.6">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6102,7 +6099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.75">
+    <row r="198" spans="1:8" ht="15.6">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6154,7 +6151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75">
+    <row r="200" spans="1:8" ht="15.6">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6180,7 +6177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75">
+    <row r="201" spans="1:8" ht="15.6">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6206,7 +6203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75">
+    <row r="202" spans="1:8" ht="15.6">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6232,7 +6229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75">
+    <row r="203" spans="1:8" ht="15.6">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6259,7 +6256,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="62" t="s">
+      <c r="A205" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6285,7 +6282,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="62"/>
+      <c r="A206" s="72"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6308,7 +6305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75">
+    <row r="207" spans="1:8" ht="15.6">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6334,7 +6331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75">
+    <row r="208" spans="1:8" ht="15.6">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75">
+    <row r="210" spans="1:8" ht="15.6">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6412,7 +6409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="47.25">
+    <row r="211" spans="1:8" ht="31.2">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6464,7 +6461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.75">
+    <row r="213" spans="1:8" ht="15.6">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6490,7 +6487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75">
+    <row r="214" spans="1:8" ht="15.6">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6516,7 +6513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75">
+    <row r="215" spans="1:8" ht="15.6">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6542,7 +6539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75">
+    <row r="216" spans="1:8" ht="15.6">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6568,7 +6565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75">
+    <row r="217" spans="1:8" ht="15.6">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6620,7 +6617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15">
+    <row r="219" spans="1:8">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6631,7 +6628,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="62" t="s">
+      <c r="A220" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6657,7 +6654,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="62"/>
+      <c r="A221" s="72"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6706,7 +6703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75">
+    <row r="223" spans="1:8" ht="15.6">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6732,7 +6729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75">
+    <row r="224" spans="1:8" ht="15.6">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6758,7 +6755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75">
+    <row r="225" spans="1:8" ht="15.6">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6784,7 +6781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="47.25">
+    <row r="226" spans="1:8" ht="31.2">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6810,7 +6807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.75">
+    <row r="227" spans="1:8" ht="15.6">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6836,7 +6833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75">
+    <row r="228" spans="1:8" ht="15.6">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6888,7 +6885,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.75">
+    <row r="230" spans="1:8" ht="15.6">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75">
+    <row r="231" spans="1:8" ht="15.6">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6966,7 +6963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.75">
+    <row r="233" spans="1:8" ht="15.6">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6993,7 +6990,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="62" t="s">
+      <c r="A235" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7019,7 +7016,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="62"/>
+      <c r="A236" s="72"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7042,7 +7039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.75">
+    <row r="237" spans="1:8" ht="15.6">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7068,7 +7065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.75">
+    <row r="238" spans="1:8" ht="15.6">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7094,7 +7091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.75">
+    <row r="239" spans="1:8" ht="15.6">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7120,7 +7117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="47.25">
+    <row r="240" spans="1:8" ht="31.2">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7146,7 +7143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.75">
+    <row r="241" spans="1:8" ht="15.6">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7172,7 +7169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.75">
+    <row r="242" spans="1:8" ht="15.6">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7198,7 +7195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.75">
+    <row r="243" spans="1:8" ht="15.6">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7224,7 +7221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.75">
+    <row r="244" spans="1:8" ht="15.6">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7250,7 +7247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.75">
+    <row r="245" spans="1:8" ht="15.6">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7276,7 +7273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.75">
+    <row r="246" spans="1:8" ht="15.6">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7302,7 +7299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.75">
+    <row r="247" spans="1:8" ht="15.6">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7328,7 +7325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.75">
+    <row r="248" spans="1:8" ht="15.6">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7355,7 +7352,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="62" t="s">
+      <c r="A250" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7381,7 +7378,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="62"/>
+      <c r="A251" s="72"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7404,7 +7401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.75">
+    <row r="252" spans="1:8" ht="15.6">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7430,7 +7427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.75">
+    <row r="253" spans="1:8" ht="15.6">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7456,7 +7453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.75">
+    <row r="254" spans="1:8" ht="15.6">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7482,7 +7479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.75">
+    <row r="255" spans="1:8" ht="15.6">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7508,7 +7505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.75">
+    <row r="256" spans="1:8" ht="15.6">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7534,7 +7531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.75">
+    <row r="257" spans="1:8" ht="15.6">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7560,7 +7557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.75">
+    <row r="258" spans="1:8" ht="15.6">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7586,7 +7583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.75">
+    <row r="259" spans="1:8" ht="15.6">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7612,7 +7609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.75">
+    <row r="260" spans="1:8" ht="15.6">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7638,7 +7635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.75">
+    <row r="261" spans="1:8" ht="15.6">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7664,7 +7661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.75">
+    <row r="262" spans="1:8" ht="15.6">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7690,7 +7687,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.75">
+    <row r="263" spans="1:8" ht="15.6">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7717,7 +7714,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="62" t="s">
+      <c r="A265" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7743,7 +7740,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="63"/>
+      <c r="A266" s="75"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7766,7 +7763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.75">
+    <row r="267" spans="1:8" ht="15.6">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7792,7 +7789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.75">
+    <row r="268" spans="1:8" ht="15.6">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7818,7 +7815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.75">
+    <row r="269" spans="1:8" ht="15.6">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7844,7 +7841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.75">
+    <row r="270" spans="1:8" ht="15.6">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7870,7 +7867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="47.25">
+    <row r="271" spans="1:8" ht="31.2">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -7896,7 +7893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.75">
+    <row r="272" spans="1:8" ht="15.6">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -7922,7 +7919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.75">
+    <row r="273" spans="1:8" ht="15.6">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -7948,7 +7945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.75">
+    <row r="274" spans="1:8" ht="15.6">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -7974,7 +7971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.75">
+    <row r="275" spans="1:8" ht="15.6">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -8000,7 +7997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.75">
+    <row r="276" spans="1:8" ht="15.6">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -8026,7 +8023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.75">
+    <row r="277" spans="1:8" ht="15.6">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -8053,7 +8050,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="65" t="s">
+      <c r="A279" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8079,7 +8076,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="65"/>
+      <c r="A280" s="76"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8102,7 +8099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.75">
+    <row r="281" spans="1:8" ht="15.6">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8128,7 +8125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.75">
+    <row r="282" spans="1:8" ht="15.6">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8154,7 +8151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="47.25">
+    <row r="283" spans="1:8" ht="31.2">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8180,7 +8177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.75">
+    <row r="284" spans="1:8" ht="15.6">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8206,7 +8203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.75">
+    <row r="285" spans="1:8" ht="15.6">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8232,7 +8229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.75">
+    <row r="286" spans="1:8" ht="15.6">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8258,7 +8255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.75">
+    <row r="287" spans="1:8" ht="15.6">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8284,7 +8281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.75">
+    <row r="288" spans="1:8" ht="15.6">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8310,7 +8307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.75">
+    <row r="289" spans="1:8" ht="15.6">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8336,7 +8333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.75">
+    <row r="290" spans="1:8" ht="15.6">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8362,7 +8359,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.75">
+    <row r="291" spans="1:8" ht="15.6">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8389,7 +8386,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="62" t="s">
+      <c r="A293" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8415,7 +8412,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="63"/>
+      <c r="A294" s="75"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8438,7 +8435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="15.75">
+    <row r="295" spans="1:8" ht="15.6">
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
@@ -8464,7 +8461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="47.25">
+    <row r="296" spans="1:8" ht="31.2">
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
@@ -8490,7 +8487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="31.5">
+    <row r="297" spans="1:8" ht="31.2">
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
@@ -8516,7 +8513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="15.75">
+    <row r="298" spans="1:8" ht="15.6">
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
@@ -8542,7 +8539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="15.75">
+    <row r="299" spans="1:8" ht="15.6">
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
@@ -8568,7 +8565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="15.75">
+    <row r="300" spans="1:8" ht="15.6">
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
@@ -8594,7 +8591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="15.75">
+    <row r="301" spans="1:8" ht="15.6">
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
@@ -8620,7 +8617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="15.75">
+    <row r="302" spans="1:8" ht="15.6">
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
@@ -8646,7 +8643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15.75">
+    <row r="303" spans="1:8" ht="15.6">
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
@@ -8672,7 +8669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="15.75">
+    <row r="304" spans="1:8" ht="15.6">
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
@@ -8698,7 +8695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="15.75">
+    <row r="305" spans="1:8" ht="15.6">
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
@@ -8725,286 +8722,286 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6">
-      <c r="A307" s="79" t="s">
+      <c r="A307" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B307" s="70">
+      <c r="B307" s="62">
         <v>46286</v>
       </c>
-      <c r="C307" s="70">
+      <c r="C307" s="62">
         <v>46287</v>
       </c>
-      <c r="D307" s="70">
+      <c r="D307" s="62">
         <v>46288</v>
       </c>
-      <c r="E307" s="70">
+      <c r="E307" s="62">
         <v>46289</v>
       </c>
-      <c r="F307" s="70">
+      <c r="F307" s="62">
         <v>46290</v>
       </c>
-      <c r="G307" s="70">
+      <c r="G307" s="62">
         <v>46291</v>
       </c>
-      <c r="H307" s="70">
+      <c r="H307" s="62">
         <v>46292</v>
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6">
-      <c r="A308" s="80"/>
-      <c r="B308" s="71" t="s">
+      <c r="A308" s="79"/>
+      <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C308" s="71" t="s">
+      <c r="C308" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D308" s="71" t="s">
+      <c r="D308" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="E308" s="71" t="s">
+      <c r="E308" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F308" s="71" t="s">
+      <c r="F308" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="G308" s="71" t="s">
+      <c r="G308" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="H308" s="71" t="s">
+      <c r="H308" s="63" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:8" ht="31.2">
-      <c r="A309" s="72" t="s">
+      <c r="A309" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B309" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C309" s="73" t="s">
+      <c r="B309" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C309" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="D309" s="73" t="s">
+      <c r="D309" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E309" s="73" t="s">
+      <c r="E309" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F309" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G309" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="H309" s="73" t="s">
+      <c r="F309" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G309" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H309" s="64" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="310" spans="1:8" ht="15.6">
-      <c r="A310" s="72" t="s">
+      <c r="A310" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B310" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C310" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D310" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E310" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F310" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G310" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="H310" s="74" t="s">
+      <c r="B310" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C310" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D310" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F310" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G310" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H310" s="65" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:8" ht="15.6">
-      <c r="A311" s="72" t="s">
+      <c r="A311" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B311" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C311" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D311" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E311" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F311" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G311" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="H311" s="73" t="s">
+      <c r="B311" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C311" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D311" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F311" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G311" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H311" s="64" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="312" spans="1:8" ht="15.6">
-      <c r="A312" s="75" t="s">
+      <c r="A312" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B312" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C312" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D312" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E312" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F312" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G312" s="73" t="s">
+      <c r="B312" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C312" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D312" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F312" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G312" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="H312" s="74" t="s">
+      <c r="H312" s="65" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="313" spans="1:8" ht="15.6">
-      <c r="A313" s="72" t="s">
+      <c r="A313" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B313" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C313" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D313" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E313" s="76" t="s">
+      <c r="B313" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C313" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D313" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="F313" s="76" t="s">
+      <c r="F313" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="G313" s="76" t="s">
+      <c r="G313" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H313" s="76" t="s">
+      <c r="H313" s="67" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="314" spans="1:8" ht="15.6">
-      <c r="A314" s="72" t="s">
+      <c r="A314" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B314" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="C314" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D314" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E314" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F314" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G314" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="H314" s="73" t="s">
+      <c r="B314" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C314" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D314" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E314" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F314" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" s="64" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="315" spans="1:8" ht="15.6">
-      <c r="A315" s="72" t="s">
+      <c r="A315" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B315" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="C315" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D315" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E315" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F315" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G315" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="H315" s="73" t="s">
+      <c r="B315" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C315" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D315" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E315" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F315" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" s="64" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="316" spans="1:8" ht="15.6">
-      <c r="A316" s="72" t="s">
+      <c r="A316" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="C316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="D316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="E316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="F316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="G316" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="H316" s="74" t="s">
+      <c r="B316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G316" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H316" s="65" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="317" spans="1:8" ht="15.6">
-      <c r="A317" s="72" t="s">
+      <c r="A317" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B317" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="C317" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D317" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E317" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F317" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G317" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="H317" s="74" t="s">
+      <c r="B317" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D317" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E317" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F317" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G317" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H317" s="65" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9012,56 +9009,66 @@
       <c r="A318" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="B318" s="73" t="s">
+      <c r="B318" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C318" s="73" t="s">
+      <c r="C318" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="D318" s="73" t="s">
+      <c r="D318" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="E318" s="73" t="s">
+      <c r="E318" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F318" s="76" t="s">
+      <c r="F318" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="G318" s="76" t="s">
+      <c r="G318" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H318" s="76" t="s">
+      <c r="H318" s="67" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="319" spans="1:8" ht="15.6">
-      <c r="A319" s="72" t="s">
+      <c r="A319" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B319" s="73" t="s">
+      <c r="B319" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C319" s="73" t="s">
+      <c r="C319" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="D319" s="73" t="s">
+      <c r="D319" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="E319" s="73" t="s">
+      <c r="E319" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F319" s="73" t="s">
+      <c r="F319" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="G319" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="H319" s="78" t="s">
+      <c r="G319" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H319" s="68" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
@@ -9072,17 +9079,7 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A293:A294"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
   </mergeCells>
@@ -9093,17 +9090,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -9304,6 +9290,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9314,17 +9311,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9343,6 +9329,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2142ED8-0258-412C-852C-3A508DF4CFD9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473D006C-465C-49FB-B9A3-30EB1F7F72FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +324,17 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -501,7 +512,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -687,17 +698,11 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -705,20 +710,41 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -754,7 +780,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>195</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
+      <xdr:rowOff>94615</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1111,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O319"/>
+  <dimension ref="A1:O333"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
@@ -1124,7 +1150,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1171,7 +1197,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="74"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1686,7 +1712,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1712,7 +1738,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6">
-      <c r="A15" s="74"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1996,7 +2022,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2022,7 +2048,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6">
-      <c r="A28" s="74"/>
+      <c r="A28" s="72"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2306,7 +2332,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2332,7 +2358,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="71"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2616,7 +2642,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2642,7 +2668,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6">
-      <c r="A54" s="71"/>
+      <c r="A54" s="70"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2926,7 +2952,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6">
-      <c r="A66" s="71" t="s">
+      <c r="A66" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2952,7 +2978,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6">
-      <c r="A67" s="71"/>
+      <c r="A67" s="70"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3236,7 +3262,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3262,7 +3288,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6">
-      <c r="A80" s="71"/>
+      <c r="A80" s="70"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3382,8 +3408,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="69"/>
-      <c r="H84" s="70"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="76"/>
     </row>
     <row r="85" spans="1:8" ht="15.6">
       <c r="A85" s="3" t="s">
@@ -3542,7 +3568,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3568,7 +3594,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6">
-      <c r="A93" s="71"/>
+      <c r="A93" s="70"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3826,7 +3852,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6">
-      <c r="A104" s="71" t="s">
+      <c r="A104" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3852,7 +3878,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6">
-      <c r="A105" s="71"/>
+      <c r="A105" s="70"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4110,7 +4136,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6">
-      <c r="A116" s="71" t="s">
+      <c r="A116" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4136,7 +4162,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6">
-      <c r="A117" s="71"/>
+      <c r="A117" s="70"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4808,7 +4834,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6">
-      <c r="A145" s="71" t="s">
+      <c r="A145" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4834,7 +4860,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6">
-      <c r="A146" s="71"/>
+      <c r="A146" s="70"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5170,7 +5196,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6">
-      <c r="A160" s="71" t="s">
+      <c r="A160" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5196,7 +5222,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6">
-      <c r="A161" s="71"/>
+      <c r="A161" s="70"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5532,7 +5558,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6">
-      <c r="A175" s="71" t="s">
+      <c r="A175" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5558,7 +5584,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6">
-      <c r="A176" s="71"/>
+      <c r="A176" s="70"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5894,7 +5920,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6">
-      <c r="A190" s="71" t="s">
+      <c r="A190" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5920,7 +5946,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6">
-      <c r="A191" s="71"/>
+      <c r="A191" s="70"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6256,7 +6282,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="72" t="s">
+      <c r="A205" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6282,7 +6308,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="72"/>
+      <c r="A206" s="77"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6628,7 +6654,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="72" t="s">
+      <c r="A220" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6654,7 +6680,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="72"/>
+      <c r="A221" s="77"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6990,7 +7016,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="72" t="s">
+      <c r="A235" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7016,7 +7042,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="72"/>
+      <c r="A236" s="77"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7352,7 +7378,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="72" t="s">
+      <c r="A250" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7378,7 +7404,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="72"/>
+      <c r="A251" s="77"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7714,7 +7740,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="72" t="s">
+      <c r="A265" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7740,7 +7766,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="75"/>
+      <c r="A266" s="78"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8050,7 +8076,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="76" t="s">
+      <c r="A279" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8076,7 +8102,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="76"/>
+      <c r="A280" s="79"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8386,7 +8412,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="72" t="s">
+      <c r="A293" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8412,7 +8438,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="75"/>
+      <c r="A294" s="78"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8722,7 +8748,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6">
-      <c r="A307" s="78" t="s">
+      <c r="A307" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8748,7 +8774,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6">
-      <c r="A308" s="79"/>
+      <c r="A308" s="74"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9006,7 +9032,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" ht="15.6">
-      <c r="A318" s="77" t="s">
+      <c r="A318" s="69" t="s">
         <v>27</v>
       </c>
       <c r="B318" s="64" t="s">
@@ -9057,18 +9083,345 @@
         <v>34</v>
       </c>
     </row>
+    <row r="321" spans="1:8" ht="15.6">
+      <c r="A321" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B321" s="62">
+        <v>46293</v>
+      </c>
+      <c r="C321" s="62">
+        <v>46294</v>
+      </c>
+      <c r="D321" s="62">
+        <v>46295</v>
+      </c>
+      <c r="E321" s="62">
+        <v>46296</v>
+      </c>
+      <c r="F321" s="62">
+        <v>46297</v>
+      </c>
+      <c r="G321" s="62">
+        <v>46298</v>
+      </c>
+      <c r="H321" s="62">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" ht="15.6">
+      <c r="A322" s="80"/>
+      <c r="B322" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C322" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D322" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E322" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="F322" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="G322" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="H322" s="63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="31.2">
+      <c r="A323" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="B323" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C323" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="D323" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="E323" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="F323" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G323" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="H323" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="15.6">
+      <c r="A324" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C324" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D324" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F324" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G324" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H324" s="82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="15.6">
+      <c r="A325" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B325" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C325" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D325" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E325" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F325" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G325" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="H325" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="15.6">
+      <c r="A326" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="B326" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C326" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E326" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F326" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G326" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H326" s="82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="15.6">
+      <c r="A327" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B327" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C327" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E327" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F327" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G327" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="H327" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="15.6">
+      <c r="A328" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B328" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D328" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F328" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="G328" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H328" s="82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="15.6">
+      <c r="A329" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="B329" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D329" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E329" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F329" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="G329" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="H329" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" ht="15.6">
+      <c r="A330" s="81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G330" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="H330" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="15.6">
+      <c r="A331" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B331" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C331" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D331" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F331" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G331" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H331" s="82" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" ht="15.6">
+      <c r="A332" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="B332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G332" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H332" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" ht="15.6">
+      <c r="A333" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B333" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="C333" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="D333" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="E333" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="F333" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G333" s="84" t="s">
+        <v>34</v>
+      </c>
+      <c r="H333" s="65" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="24">
+    <mergeCell ref="A321:A322"/>
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
@@ -9082,6 +9435,16 @@
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9090,6 +9453,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -9290,17 +9664,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9311,6 +9674,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9329,17 +9703,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473D006C-465C-49FB-B9A3-30EB1F7F72FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF00E09-9EDF-4001-8AE8-1DB09CE2187B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +336,19 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -512,7 +525,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -701,14 +714,20 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -722,6 +741,9 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -731,19 +753,22 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1137,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O333"/>
+  <dimension ref="A1:O347"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
@@ -1150,7 +1175,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1197,7 +1222,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="72"/>
+      <c r="A2" s="84"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1712,7 +1737,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1738,7 +1763,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6">
-      <c r="A15" s="72"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2022,7 +2047,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2048,7 +2073,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6">
-      <c r="A28" s="72"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2332,7 +2357,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2358,7 +2383,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="70"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2642,7 +2667,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6">
-      <c r="A53" s="70" t="s">
+      <c r="A53" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2668,7 +2693,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6">
-      <c r="A54" s="70"/>
+      <c r="A54" s="79"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2952,7 +2977,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6">
-      <c r="A66" s="70" t="s">
+      <c r="A66" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2978,7 +3003,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6">
-      <c r="A67" s="70"/>
+      <c r="A67" s="79"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3262,7 +3287,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6">
-      <c r="A79" s="70" t="s">
+      <c r="A79" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3288,7 +3313,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6">
-      <c r="A80" s="70"/>
+      <c r="A80" s="79"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3408,8 +3433,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="75"/>
-      <c r="H84" s="76"/>
+      <c r="G84" s="77"/>
+      <c r="H84" s="78"/>
     </row>
     <row r="85" spans="1:8" ht="15.6">
       <c r="A85" s="3" t="s">
@@ -3568,7 +3593,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3594,7 +3619,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6">
-      <c r="A93" s="70"/>
+      <c r="A93" s="79"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3852,7 +3877,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6">
-      <c r="A104" s="70" t="s">
+      <c r="A104" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3878,7 +3903,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6">
-      <c r="A105" s="70"/>
+      <c r="A105" s="79"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4136,7 +4161,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6">
-      <c r="A116" s="70" t="s">
+      <c r="A116" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4162,7 +4187,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6">
-      <c r="A117" s="70"/>
+      <c r="A117" s="79"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4834,7 +4859,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6">
-      <c r="A145" s="70" t="s">
+      <c r="A145" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4860,7 +4885,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6">
-      <c r="A146" s="70"/>
+      <c r="A146" s="79"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5196,7 +5221,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6">
-      <c r="A160" s="70" t="s">
+      <c r="A160" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5222,7 +5247,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6">
-      <c r="A161" s="70"/>
+      <c r="A161" s="79"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5558,7 +5583,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6">
-      <c r="A175" s="70" t="s">
+      <c r="A175" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5584,7 +5609,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6">
-      <c r="A176" s="70"/>
+      <c r="A176" s="79"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5920,7 +5945,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6">
-      <c r="A190" s="70" t="s">
+      <c r="A190" s="79" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5946,7 +5971,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6">
-      <c r="A191" s="70"/>
+      <c r="A191" s="79"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6282,7 +6307,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="77" t="s">
+      <c r="A205" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6308,7 +6333,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="77"/>
+      <c r="A206" s="80"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6654,7 +6679,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="77" t="s">
+      <c r="A220" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6680,7 +6705,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="77"/>
+      <c r="A221" s="80"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -7016,7 +7041,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="77" t="s">
+      <c r="A235" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7042,7 +7067,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="77"/>
+      <c r="A236" s="80"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7378,7 +7403,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="77" t="s">
+      <c r="A250" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7404,7 +7429,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="77"/>
+      <c r="A251" s="80"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7740,7 +7765,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="77" t="s">
+      <c r="A265" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7766,7 +7791,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="78"/>
+      <c r="A266" s="81"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8076,7 +8101,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="79" t="s">
+      <c r="A279" s="82" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8102,7 +8127,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="79"/>
+      <c r="A280" s="82"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8412,7 +8437,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="77" t="s">
+      <c r="A293" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8438,7 +8463,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="78"/>
+      <c r="A294" s="81"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8748,7 +8773,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6">
-      <c r="A307" s="73" t="s">
+      <c r="A307" s="75" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8774,7 +8799,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6">
-      <c r="A308" s="74"/>
+      <c r="A308" s="76"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9084,7 +9109,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="15.6">
-      <c r="A321" s="80" t="s">
+      <c r="A321" s="74" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9110,7 +9135,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="15.6">
-      <c r="A322" s="80"/>
+      <c r="A322" s="74"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9134,25 +9159,25 @@
       </c>
     </row>
     <row r="323" spans="1:8" ht="31.2">
-      <c r="A323" s="81" t="s">
+      <c r="A323" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B323" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C323" s="82" t="s">
+      <c r="B323" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C323" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="D323" s="82" t="s">
+      <c r="D323" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="E323" s="82" t="s">
+      <c r="E323" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="F323" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="G323" s="82" t="s">
+      <c r="F323" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G323" s="71" t="s">
         <v>11</v>
       </c>
       <c r="H323" s="65" t="s">
@@ -9160,51 +9185,51 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="15.6">
-      <c r="A324" s="81" t="s">
+      <c r="A324" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B324" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C324" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D324" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E324" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F324" s="82" t="s">
+      <c r="B324" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C324" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D324" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F324" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G324" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="H324" s="82" t="s">
+      <c r="H324" s="71" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="325" spans="1:8" ht="15.6">
-      <c r="A325" s="81" t="s">
+      <c r="A325" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B325" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C325" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D325" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E325" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F325" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="G325" s="82" t="s">
+      <c r="B325" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C325" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D325" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E325" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F325" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G325" s="71" t="s">
         <v>11</v>
       </c>
       <c r="H325" s="65" t="s">
@@ -9212,33 +9237,33 @@
       </c>
     </row>
     <row r="326" spans="1:8" ht="15.6">
-      <c r="A326" s="81" t="s">
+      <c r="A326" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B326" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C326" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D326" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E326" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F326" s="82" t="s">
+      <c r="B326" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C326" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E326" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F326" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G326" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="H326" s="82" t="s">
+      <c r="H326" s="71" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="327" spans="1:8" ht="15.6">
-      <c r="A327" s="81" t="s">
+      <c r="A327" s="70" t="s">
         <v>22</v>
       </c>
       <c r="B327" s="25" t="s">
@@ -9250,13 +9275,13 @@
       <c r="D327" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E327" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F327" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="G327" s="82" t="s">
+      <c r="E327" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F327" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G327" s="71" t="s">
         <v>9</v>
       </c>
       <c r="H327" s="65" t="s">
@@ -9264,51 +9289,51 @@
       </c>
     </row>
     <row r="328" spans="1:8" ht="15.6">
-      <c r="A328" s="81" t="s">
+      <c r="A328" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B328" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C328" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="D328" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="E328" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F328" s="82" t="s">
+      <c r="B328" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D328" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F328" s="71" t="s">
         <v>11</v>
       </c>
       <c r="G328" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="H328" s="82" t="s">
+      <c r="H328" s="71" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="329" spans="1:8" ht="15.6">
-      <c r="A329" s="81" t="s">
+      <c r="A329" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B329" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C329" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="D329" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="E329" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F329" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="G329" s="82" t="s">
+      <c r="B329" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D329" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E329" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F329" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G329" s="71" t="s">
         <v>9</v>
       </c>
       <c r="H329" s="65" t="s">
@@ -9316,25 +9341,25 @@
       </c>
     </row>
     <row r="330" spans="1:8" ht="15.6">
-      <c r="A330" s="81" t="s">
+      <c r="A330" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B330" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="C330" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="D330" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="E330" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="F330" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G330" s="82" t="s">
+      <c r="B330" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C330" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D330" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E330" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F330" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G330" s="71" t="s">
         <v>13</v>
       </c>
       <c r="H330" s="65" t="s">
@@ -9342,33 +9367,33 @@
       </c>
     </row>
     <row r="331" spans="1:8" ht="15.6">
-      <c r="A331" s="81" t="s">
+      <c r="A331" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B331" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C331" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D331" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E331" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F331" s="82" t="s">
+      <c r="B331" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C331" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D331" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F331" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G331" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="H331" s="82" t="s">
+      <c r="H331" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="15.6">
-      <c r="A332" s="83" t="s">
+      <c r="A332" s="72" t="s">
         <v>27</v>
       </c>
       <c r="B332" s="25" t="s">
@@ -9394,33 +9419,380 @@
       </c>
     </row>
     <row r="333" spans="1:8" ht="15.6">
-      <c r="A333" s="81" t="s">
+      <c r="A333" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B333" s="82" t="s">
+      <c r="B333" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C333" s="82" t="s">
+      <c r="C333" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="D333" s="82" t="s">
+      <c r="D333" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E333" s="82" t="s">
+      <c r="E333" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="F333" s="82" t="s">
+      <c r="F333" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="G333" s="84" t="s">
+      <c r="G333" s="73" t="s">
         <v>34</v>
       </c>
       <c r="H333" s="65" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="335" spans="1:8" ht="15.6">
+      <c r="A335" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B335" s="47">
+        <v>46300</v>
+      </c>
+      <c r="C335" s="47">
+        <v>46301</v>
+      </c>
+      <c r="D335" s="47">
+        <v>46302</v>
+      </c>
+      <c r="E335" s="47">
+        <v>46303</v>
+      </c>
+      <c r="F335" s="47">
+        <v>46304</v>
+      </c>
+      <c r="G335" s="47">
+        <v>46305</v>
+      </c>
+      <c r="H335" s="47">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" ht="15.6">
+      <c r="A336" s="81"/>
+      <c r="B336" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C336" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D336" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E336" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F336" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G336" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H336" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" ht="28.8">
+      <c r="A337" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B337" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C337" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D337" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="E337" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="F337" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G337" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="H337" s="85" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" ht="15.6">
+      <c r="A338" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B338" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C338" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D338" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F338" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G338" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="H338" s="85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" ht="15.6">
+      <c r="A339" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B339" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C339" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D339" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E339" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F339" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G339" s="85" t="s">
+        <v>26</v>
+      </c>
+      <c r="H339" s="86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" ht="15.6">
+      <c r="A340" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B340" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C340" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D340" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E340" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F340" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G340" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="H340" s="86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" ht="15.6">
+      <c r="A341" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B341" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C341" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D341" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E341" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F341" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G341" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H341" s="87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" ht="15.6">
+      <c r="A342" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B342" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C342" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D342" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E342" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F342" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G342" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H342" s="87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" ht="15.6">
+      <c r="A343" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C343" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D343" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F343" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="G343" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H343" s="86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" ht="15.6">
+      <c r="A344" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B344" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C344" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E344" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F344" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="G344" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="H344" s="86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" ht="15.6">
+      <c r="A345" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B345" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C345" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D345" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E345" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F345" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="G345" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="H345" s="85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" ht="15.6">
+      <c r="A346" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="D346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="G346" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H346" s="87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" ht="15.6">
+      <c r="A347" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B347" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C347" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="D347" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E347" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="F347" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="G347" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="H347" s="85" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="A335:A336"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A321:A322"/>
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="G84:H84"/>
@@ -9435,16 +9807,6 @@
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9453,17 +9815,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -9664,6 +10015,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9674,17 +10036,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9703,6 +10054,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF00E09-9EDF-4001-8AE8-1DB09CE2187B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B072B73B-28D0-40B5-8891-A59C24753D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,6 +726,33 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -741,35 +768,8 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1163,19 +1163,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
   <dimension ref="A1:O347"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1221,8 +1221,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="84"/>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="82"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1736,8 +1736,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6">
-      <c r="A14" s="83" t="s">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1762,8 +1762,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6">
-      <c r="A15" s="84"/>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="82"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -2046,8 +2046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6">
-      <c r="A27" s="83" t="s">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2072,8 +2072,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6">
-      <c r="A28" s="84"/>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="82"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2356,8 +2356,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="79" t="s">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2382,8 +2382,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="79"/>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="80"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6">
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6">
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2666,8 +2666,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6">
-      <c r="A53" s="79" t="s">
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2692,8 +2692,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6">
-      <c r="A54" s="79"/>
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="80"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6">
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6">
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6">
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6">
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6">
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6">
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6">
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6">
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6">
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2976,8 +2976,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6">
-      <c r="A66" s="79" t="s">
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -3002,8 +3002,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6">
-      <c r="A67" s="79"/>
+    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="80"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6">
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6">
+    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6">
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6">
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6">
+    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6">
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6">
+    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3286,8 +3286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6">
-      <c r="A79" s="79" t="s">
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3312,8 +3312,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6">
-      <c r="A80" s="79"/>
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="80"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6">
+    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6">
+    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6">
+    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6">
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3433,10 +3433,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="77"/>
-      <c r="H84" s="78"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6">
+      <c r="G84" s="86"/>
+      <c r="H84" s="87"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6">
+    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6">
+    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6">
+    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6">
+    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6">
+    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3592,8 +3592,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6">
-      <c r="A92" s="79" t="s">
+    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3618,8 +3618,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6">
-      <c r="A93" s="79"/>
+    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="80"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6">
+    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6">
+    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6">
+    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6">
+    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6">
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6">
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6">
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6">
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6">
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3876,8 +3876,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6">
-      <c r="A104" s="79" t="s">
+    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3902,8 +3902,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6">
-      <c r="A105" s="79"/>
+    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="80"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6">
+    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6">
+    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6">
+    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6">
+    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6">
+    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6">
+    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6">
+    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6">
+    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6">
+    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4160,8 +4160,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6">
-      <c r="A116" s="79" t="s">
+    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4186,8 +4186,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6">
-      <c r="A117" s="79"/>
+    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="80"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6">
+    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6">
+    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6">
+    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6">
+    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6">
+    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6">
+    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6">
+    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6">
+    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6">
+    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6">
+    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6">
+    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6">
+    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6">
+    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4546,7 +4546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6">
+    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6">
+    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6">
+    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6">
+    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6">
+    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6">
+    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6">
+    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6">
+    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6">
+    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6">
+    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6">
+    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6">
+    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4858,8 +4858,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6">
-      <c r="A145" s="79" t="s">
+    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A145" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4884,8 +4884,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6">
-      <c r="A146" s="79"/>
+    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="80"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6">
+    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6">
+    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6">
+    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6">
+    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6">
+    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6">
+    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6">
+    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6">
+    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6">
+    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6">
+    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6">
+    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6">
+    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5220,8 +5220,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6">
-      <c r="A160" s="79" t="s">
+    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A160" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5246,8 +5246,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6">
-      <c r="A161" s="79"/>
+    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A161" s="80"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6">
+    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6">
+    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6">
+    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6">
+    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6">
+    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6">
+    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6">
+    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6">
+    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6">
+    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6">
+    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6">
+    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6">
+    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5582,8 +5582,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6">
-      <c r="A175" s="79" t="s">
+    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5608,8 +5608,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6">
-      <c r="A176" s="79"/>
+    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A176" s="80"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6">
+    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6">
+    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6">
+    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6">
+    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6">
+    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6">
+    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6">
+    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6">
+    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6">
+    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6">
+    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6">
+    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6">
+    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5944,8 +5944,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.6">
-      <c r="A190" s="79" t="s">
+    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A190" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5970,8 +5970,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.6">
-      <c r="A191" s="79"/>
+    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A191" s="80"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.6">
+    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.6">
+    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.6">
+    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.6">
+    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.6">
+    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.6">
+    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.6">
+    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.6">
+    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.6">
+    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.6">
+    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.6">
+    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.6">
+    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6306,8 +6306,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="80" t="s">
+    <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A205" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6332,8 +6332,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="80"/>
+    <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A206" s="78"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.6">
+    <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.6">
+    <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.8">
+    <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.6">
+    <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="31.2">
+    <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="31.2">
+    <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.6">
+    <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.6">
+    <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.6">
+    <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.6">
+    <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.6">
+    <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.6">
+    <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6678,8 +6678,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="80" t="s">
+    <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A220" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6704,8 +6704,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="80"/>
+    <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A221" s="78"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.6">
+    <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.6">
+    <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.6">
+    <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.6">
+    <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="31.2">
+    <row r="226" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.6">
+    <row r="227" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.6">
+    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.6">
+    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.6">
+    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.6">
+    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.6">
+    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.6">
+    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -7040,8 +7040,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="80" t="s">
+    <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A235" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7066,8 +7066,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="80"/>
+    <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A236" s="78"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.6">
+    <row r="237" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.6">
+    <row r="238" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.6">
+    <row r="239" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="31.2">
+    <row r="240" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.6">
+    <row r="241" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.6">
+    <row r="242" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.6">
+    <row r="243" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.6">
+    <row r="244" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.6">
+    <row r="245" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.6">
+    <row r="246" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.6">
+    <row r="247" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.6">
+    <row r="248" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7402,8 +7402,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="80" t="s">
+    <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A250" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7428,8 +7428,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="80"/>
+    <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A251" s="78"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.6">
+    <row r="252" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.6">
+    <row r="253" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.6">
+    <row r="254" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.6">
+    <row r="255" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.6">
+    <row r="256" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.6">
+    <row r="257" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.6">
+    <row r="258" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.6">
+    <row r="259" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.6">
+    <row r="260" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.6">
+    <row r="261" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.6">
+    <row r="262" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.6">
+    <row r="263" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7764,8 +7764,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="80" t="s">
+    <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A265" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7790,8 +7790,8 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="81"/>
+    <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A266" s="79"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.6">
+    <row r="267" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.6">
+    <row r="268" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.6">
+    <row r="269" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.6">
+    <row r="270" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="31.2">
+    <row r="271" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.6">
+    <row r="272" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.6">
+    <row r="273" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.6">
+    <row r="274" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.6">
+    <row r="275" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.6">
+    <row r="276" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.6">
+    <row r="277" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -8100,8 +8100,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="82" t="s">
+    <row r="279" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A279" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8126,8 +8126,8 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="82"/>
+    <row r="280" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A280" s="88"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.6">
+    <row r="281" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.6">
+    <row r="282" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="31.2">
+    <row r="283" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.6">
+    <row r="284" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.6">
+    <row r="285" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.6">
+    <row r="286" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.6">
+    <row r="287" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.6">
+    <row r="288" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.6">
+    <row r="289" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.6">
+    <row r="290" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.6">
+    <row r="291" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8436,8 +8436,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="80" t="s">
+    <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A293" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8462,8 +8462,8 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="81"/>
+    <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A294" s="79"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="15.6">
+    <row r="295" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="31.2">
+    <row r="296" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="31.2">
+    <row r="297" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="15.6">
+    <row r="298" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="15.6">
+    <row r="299" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="15.6">
+    <row r="300" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="15.6">
+    <row r="301" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="15.6">
+    <row r="302" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15.6">
+    <row r="303" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="15.6">
+    <row r="304" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="15.6">
+    <row r="305" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
@@ -8772,8 +8772,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="15.6">
-      <c r="A307" s="75" t="s">
+    <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A307" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8798,8 +8798,8 @@
         <v>46292</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="15.6">
-      <c r="A308" s="76"/>
+    <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A308" s="85"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="31.2">
+    <row r="309" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A309" s="66" t="s">
         <v>17</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="15.6">
+    <row r="310" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A310" s="66" t="s">
         <v>20</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="15.6">
+    <row r="311" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A311" s="66" t="s">
         <v>8</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="15.6">
+    <row r="312" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A312" s="66" t="s">
         <v>23</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="15.6">
+    <row r="313" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A313" s="66" t="s">
         <v>22</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="15.6">
+    <row r="314" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A314" s="66" t="s">
         <v>12</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="15.6">
+    <row r="315" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A315" s="66" t="s">
         <v>14</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="15.6">
+    <row r="316" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A316" s="66" t="s">
         <v>21</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="15.6">
+    <row r="317" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A317" s="66" t="s">
         <v>18</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="15.6">
+    <row r="318" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A318" s="69" t="s">
         <v>27</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="15.6">
+    <row r="319" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A319" s="66" t="s">
         <v>28</v>
       </c>
@@ -9108,8 +9108,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="15.6">
-      <c r="A321" s="74" t="s">
+    <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A321" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9134,8 +9134,8 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="15.6">
-      <c r="A322" s="74"/>
+    <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A322" s="83"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="31.2">
+    <row r="323" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A323" s="70" t="s">
         <v>17</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="15.6">
+    <row r="324" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A324" s="70" t="s">
         <v>21</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="15.6">
+    <row r="325" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A325" s="70" t="s">
         <v>8</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="15.6">
+    <row r="326" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A326" s="70" t="s">
         <v>23</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="15.6">
+    <row r="327" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A327" s="70" t="s">
         <v>22</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="15.6">
+    <row r="328" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A328" s="70" t="s">
         <v>12</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="15.6">
+    <row r="329" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A329" s="70" t="s">
         <v>20</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:8" ht="15.6">
+    <row r="330" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A330" s="70" t="s">
         <v>14</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="15.6">
+    <row r="331" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A331" s="70" t="s">
         <v>18</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:8" ht="15.6">
+    <row r="332" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A332" s="72" t="s">
         <v>27</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="15.6">
+    <row r="333" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A333" s="70" t="s">
         <v>28</v>
       </c>
@@ -9444,8 +9444,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="15.6">
-      <c r="A335" s="80" t="s">
+    <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A335" s="78" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9470,8 +9470,8 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="15.6">
-      <c r="A336" s="81"/>
+    <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A336" s="79"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9494,307 +9494,294 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="28.8">
+    <row r="337" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A337" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B337" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C337" s="85" t="s">
+      <c r="B337" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C337" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="D337" s="85" t="s">
+      <c r="D337" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="E337" s="85" t="s">
+      <c r="E337" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="F337" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G337" s="86" t="s">
-        <v>10</v>
-      </c>
-      <c r="H337" s="85" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" ht="15.6">
+      <c r="F337" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G337" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H337" s="74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A338" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B338" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C338" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="D338" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E338" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F338" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G338" s="86" t="s">
-        <v>10</v>
-      </c>
-      <c r="H338" s="85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" ht="15.6">
+      <c r="B338" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C338" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D338" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F338" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G338" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H338" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A339" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B339" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C339" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="D339" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E339" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F339" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G339" s="85" t="s">
+      <c r="B339" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C339" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D339" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E339" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F339" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G339" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="H339" s="86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" ht="15.6">
+      <c r="H339" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A340" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B340" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C340" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="D340" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E340" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F340" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G340" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="H340" s="86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" ht="15.6">
+      <c r="B340" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C340" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D340" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E340" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F340" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G340" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H340" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A341" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B341" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C341" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="D341" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E341" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F341" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G341" s="87" t="s">
+      <c r="B341" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C341" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D341" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E341" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F341" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G341" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="H341" s="87" t="s">
+      <c r="H341" s="76" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="342" spans="1:8" ht="15.6">
+    <row r="342" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A342" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B342" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="C342" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="D342" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="E342" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="F342" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="G342" s="87" t="s">
+      <c r="B342" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C342" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D342" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E342" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F342" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G342" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="H342" s="87" t="s">
+      <c r="H342" s="76" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="343" spans="1:8" ht="15.6">
+    <row r="343" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A343" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B343" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C343" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D343" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="E343" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F343" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="G343" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="H343" s="86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" ht="15.6">
+      <c r="B343" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C343" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D343" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F343" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G343" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H343" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A344" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B344" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C344" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D344" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="E344" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F344" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="G344" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H344" s="86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" ht="15.6">
+      <c r="B344" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C344" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E344" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F344" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G344" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="H344" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A345" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B345" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C345" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D345" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="E345" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F345" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="G345" s="86" t="s">
-        <v>10</v>
-      </c>
-      <c r="H345" s="85" t="s">
+      <c r="B345" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C345" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D345" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E345" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F345" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G345" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H345" s="74" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="15.6">
+    <row r="346" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A346" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B346" s="87" t="s">
+      <c r="B346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C346" s="87" t="s">
+      <c r="C346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D346" s="87" t="s">
+      <c r="D346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="E346" s="87" t="s">
+      <c r="E346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F346" s="87" t="s">
+      <c r="F346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G346" s="87" t="s">
+      <c r="G346" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="H346" s="87" t="s">
+      <c r="H346" s="76" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="347" spans="1:8" ht="15.6">
+    <row r="347" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A347" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B347" s="85" t="s">
+      <c r="B347" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="C347" s="85" t="s">
+      <c r="C347" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="D347" s="85" t="s">
+      <c r="D347" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="E347" s="85" t="s">
+      <c r="E347" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="F347" s="85" t="s">
+      <c r="F347" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="G347" s="88" t="s">
+      <c r="G347" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="H347" s="85" t="s">
+      <c r="H347" s="74" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A335:A336"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A321:A322"/>
-    <mergeCell ref="A307:A308"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
@@ -9804,6 +9791,19 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A335:A336"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A321:A322"/>
+    <mergeCell ref="A307:A308"/>
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
@@ -9815,6 +9815,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -10015,17 +10026,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10036,6 +10036,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10054,17 +10065,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B072B73B-28D0-40B5-8891-A59C24753D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAADB63-916A-46E7-933F-CA943BFEE59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -738,20 +738,26 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -761,12 +767,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1162,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O347"/>
+  <dimension ref="A1:O361"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -1175,7 +1175,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1222,7 +1222,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1737,7 +1737,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="82" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1763,7 +1763,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+      <c r="A15" s="83"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="81" t="s">
+      <c r="A27" s="82" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2073,7 +2073,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="82"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -3433,8 +3433,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="86"/>
-      <c r="H84" s="87"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="79"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -6307,7 +6307,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="78" t="s">
+      <c r="A205" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6333,7 +6333,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="78"/>
+      <c r="A206" s="81"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6679,7 +6679,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="78" t="s">
+      <c r="A220" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6705,7 +6705,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="78"/>
+      <c r="A221" s="81"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -7041,7 +7041,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="78" t="s">
+      <c r="A235" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7067,7 +7067,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="78"/>
+      <c r="A236" s="81"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7403,7 +7403,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A250" s="78" t="s">
+      <c r="A250" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7429,7 +7429,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="78"/>
+      <c r="A251" s="81"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7765,7 +7765,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="78" t="s">
+      <c r="A265" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7791,7 +7791,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="79"/>
+      <c r="A266" s="84"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8437,7 +8437,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="78" t="s">
+      <c r="A293" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8463,7 +8463,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="79"/>
+      <c r="A294" s="84"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8773,7 +8773,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="84" t="s">
+      <c r="A307" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8799,7 +8799,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A308" s="85"/>
+      <c r="A308" s="87"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9109,7 +9109,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="83" t="s">
+      <c r="A321" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9135,7 +9135,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A322" s="83"/>
+      <c r="A322" s="85"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9445,7 +9445,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A335" s="78" t="s">
+      <c r="A335" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9471,7 +9471,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A336" s="79"/>
+      <c r="A336" s="84"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9780,22 +9780,345 @@
         <v>9</v>
       </c>
     </row>
+    <row r="349" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A349" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B349" s="47">
+        <v>46307</v>
+      </c>
+      <c r="C349" s="47">
+        <v>46308</v>
+      </c>
+      <c r="D349" s="47">
+        <v>46309</v>
+      </c>
+      <c r="E349" s="47">
+        <v>46310</v>
+      </c>
+      <c r="F349" s="47">
+        <v>46311</v>
+      </c>
+      <c r="G349" s="47">
+        <v>46312</v>
+      </c>
+      <c r="H349" s="47">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A350" s="84"/>
+      <c r="B350" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C350" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D350" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E350" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F350" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G350" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H350" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A351" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B351" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C351" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="D351" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="E351" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F351" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G351" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H351" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A352" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B352" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C352" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D352" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F352" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G352" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H352" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A353" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B353" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C353" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D353" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E353" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F353" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G353" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H353" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A354" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B354" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C354" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D354" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F354" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G354" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H354" s="74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A355" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B355" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C355" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D355" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F355" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G355" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="H355" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A356" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B356" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C356" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D356" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G356" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H356" s="74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A357" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B357" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C357" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D357" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G357" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H357" s="74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A358" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G358" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H358" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A359" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G359" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="H359" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A360" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G360" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H360" s="76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A361" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B361" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C361" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D361" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E361" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F361" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G361" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H361" s="77" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="26">
+    <mergeCell ref="A349:A350"/>
     <mergeCell ref="A335:A336"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A116:A117"/>
@@ -9807,6 +10130,20 @@
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A190:A191"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9815,14 +10152,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10027,21 +10362,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10066,9 +10400,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAADB63-916A-46E7-933F-CA943BFEE59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47784282-006C-40E4-A23B-E4A66CEAA64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,6 +347,19 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -525,7 +538,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,6 +749,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1175,7 +1197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1222,7 +1244,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
+      <c r="A2" s="86"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1737,7 +1759,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1763,7 +1785,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="83"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2047,7 +2069,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="82" t="s">
+      <c r="A27" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2073,7 +2095,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="83"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2357,7 +2379,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2383,7 +2405,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="80"/>
+      <c r="A41" s="83"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2667,7 +2689,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2693,7 +2715,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="80"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2977,7 +2999,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="80" t="s">
+      <c r="A66" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -3003,7 +3025,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="80"/>
+      <c r="A67" s="83"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3287,7 +3309,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="80" t="s">
+      <c r="A79" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3313,7 +3335,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="80"/>
+      <c r="A80" s="83"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3433,8 +3455,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="78"/>
-      <c r="H84" s="79"/>
+      <c r="G84" s="81"/>
+      <c r="H84" s="82"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3593,7 +3615,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="80" t="s">
+      <c r="A92" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3619,7 +3641,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="80"/>
+      <c r="A93" s="83"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3877,7 +3899,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="80" t="s">
+      <c r="A104" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3903,7 +3925,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="80"/>
+      <c r="A105" s="83"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4161,7 +4183,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="80" t="s">
+      <c r="A116" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4187,7 +4209,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="80"/>
+      <c r="A117" s="83"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4859,7 +4881,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="80" t="s">
+      <c r="A145" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4885,7 +4907,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="80"/>
+      <c r="A146" s="83"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5221,7 +5243,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="80" t="s">
+      <c r="A160" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5247,7 +5269,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="80"/>
+      <c r="A161" s="83"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5583,7 +5605,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="80" t="s">
+      <c r="A175" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5609,7 +5631,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="80"/>
+      <c r="A176" s="83"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5945,7 +5967,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="80" t="s">
+      <c r="A190" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5971,7 +5993,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="80"/>
+      <c r="A191" s="83"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6307,7 +6329,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="81" t="s">
+      <c r="A205" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6333,7 +6355,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="81"/>
+      <c r="A206" s="84"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6679,7 +6701,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="81" t="s">
+      <c r="A220" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6705,7 +6727,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="81"/>
+      <c r="A221" s="84"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -7041,7 +7063,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="81" t="s">
+      <c r="A235" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7067,7 +7089,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="81"/>
+      <c r="A236" s="84"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7403,7 +7425,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A250" s="81" t="s">
+      <c r="A250" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7429,7 +7451,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="81"/>
+      <c r="A251" s="84"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7765,7 +7787,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="81" t="s">
+      <c r="A265" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7791,7 +7813,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="84"/>
+      <c r="A266" s="87"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8101,7 +8123,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A279" s="88" t="s">
+      <c r="A279" s="91" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8127,7 +8149,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A280" s="88"/>
+      <c r="A280" s="91"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8437,7 +8459,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="81" t="s">
+      <c r="A293" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8463,7 +8485,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="84"/>
+      <c r="A294" s="87"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8773,7 +8795,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="86" t="s">
+      <c r="A307" s="89" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8799,7 +8821,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A308" s="87"/>
+      <c r="A308" s="90"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9109,7 +9131,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="85" t="s">
+      <c r="A321" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9135,7 +9157,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A322" s="85"/>
+      <c r="A322" s="88"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9445,7 +9467,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A335" s="81" t="s">
+      <c r="A335" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9471,7 +9493,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A336" s="84"/>
+      <c r="A336" s="87"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9781,7 +9803,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A349" s="81" t="s">
+      <c r="A349" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B349" s="47">
@@ -9834,22 +9856,22 @@
       <c r="A351" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B351" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C351" s="74" t="s">
+      <c r="B351" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C351" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D351" s="74" t="s">
+      <c r="D351" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="E351" s="74" t="s">
+      <c r="E351" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="F351" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G351" s="74" t="s">
+      <c r="F351" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G351" s="78" t="s">
         <v>11</v>
       </c>
       <c r="H351" s="75" t="s">
@@ -9860,25 +9882,25 @@
       <c r="A352" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B352" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C352" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D352" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E352" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F352" s="74" t="s">
+      <c r="B352" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C352" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D352" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F352" s="78" t="s">
         <v>9</v>
       </c>
       <c r="G352" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="H352" s="74" t="s">
+      <c r="H352" s="78" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9886,22 +9908,22 @@
       <c r="A353" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B353" s="76" t="s">
+      <c r="B353" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C353" s="76" t="s">
+      <c r="C353" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D353" s="60" t="s">
+      <c r="D353" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E353" s="60" t="s">
+      <c r="E353" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F353" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="G353" s="74" t="s">
+      <c r="F353" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G353" s="78" t="s">
         <v>11</v>
       </c>
       <c r="H353" s="75" t="s">
@@ -9912,25 +9934,25 @@
       <c r="A354" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B354" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C354" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D354" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E354" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F354" s="74" t="s">
+      <c r="B354" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C354" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D354" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F354" s="78" t="s">
         <v>9</v>
       </c>
       <c r="G354" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="H354" s="74" t="s">
+      <c r="H354" s="78" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9938,22 +9960,22 @@
       <c r="A355" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B355" s="76" t="s">
+      <c r="B355" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C355" s="76" t="s">
+      <c r="C355" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D355" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E355" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F355" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G355" s="74" t="s">
+      <c r="D355" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F355" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G355" s="78" t="s">
         <v>9</v>
       </c>
       <c r="H355" s="75" t="s">
@@ -9964,25 +9986,25 @@
       <c r="A356" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B356" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="C356" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="D356" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E356" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F356" s="74" t="s">
-        <v>11</v>
+      <c r="B356" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C356" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D356" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F356" s="78" t="s">
+        <v>13</v>
       </c>
       <c r="G356" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="H356" s="74" t="s">
+      <c r="H356" s="78" t="s">
         <v>11</v>
       </c>
     </row>
@@ -9990,25 +10012,25 @@
       <c r="A357" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B357" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="C357" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="D357" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E357" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F357" s="74" t="s">
+      <c r="B357" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C357" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D357" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" s="78" t="s">
         <v>11</v>
       </c>
       <c r="G357" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="H357" s="74" t="s">
+      <c r="H357" s="78" t="s">
         <v>9</v>
       </c>
     </row>
@@ -10016,22 +10038,22 @@
       <c r="A358" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B358" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C358" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D358" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="E358" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="F358" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G358" s="74" t="s">
+      <c r="B358" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C358" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D358" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E358" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G358" s="78" t="s">
         <v>13</v>
       </c>
       <c r="H358" s="75" t="s">
@@ -10042,22 +10064,22 @@
       <c r="A359" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B359" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C359" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D359" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E359" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F359" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G359" s="74" t="s">
+      <c r="B359" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C359" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D359" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F359" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G359" s="78" t="s">
         <v>9</v>
       </c>
       <c r="H359" s="75" t="s">
@@ -10068,25 +10090,25 @@
       <c r="A360" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B360" s="76" t="s">
+      <c r="B360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C360" s="76" t="s">
+      <c r="C360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D360" s="76" t="s">
+      <c r="D360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E360" s="76" t="s">
+      <c r="E360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="F360" s="76" t="s">
+      <c r="F360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="G360" s="76" t="s">
+      <c r="G360" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="H360" s="76" t="s">
+      <c r="H360" s="79" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10094,25 +10116,25 @@
       <c r="A361" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="60" t="s">
+      <c r="B361" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C361" s="60" t="s">
+      <c r="C361" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D361" s="60" t="s">
+      <c r="D361" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E361" s="60" t="s">
+      <c r="E361" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="F361" s="60" t="s">
+      <c r="F361" s="24" t="s">
         <v>33</v>
       </c>
       <c r="G361" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="H361" s="77" t="s">
+      <c r="H361" s="80" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10152,6 +10174,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10160,7 +10193,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -10361,18 +10394,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -10380,7 +10413,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10397,15 +10430,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47784282-006C-40E4-A23B-E4A66CEAA64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{47784282-006C-40E4-A23B-E4A66CEAA64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF97B3E8-BA5D-4963-9AD3-06DA8F327181}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -760,26 +760,14 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -792,6 +780,18 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1184,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O361"/>
+  <dimension ref="A1:O375"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -1197,7 +1197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1244,7 +1244,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="86"/>
+      <c r="A2" s="89"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1785,7 +1785,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
+      <c r="A15" s="89"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="85" t="s">
+      <c r="A27" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -3455,8 +3455,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="81"/>
-      <c r="H84" s="82"/>
+      <c r="G84" s="90"/>
+      <c r="H84" s="91"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -6329,7 +6329,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="84" t="s">
+      <c r="A205" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6355,7 +6355,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="84"/>
+      <c r="A206" s="81"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6701,7 +6701,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="84" t="s">
+      <c r="A220" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6727,7 +6727,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="84"/>
+      <c r="A221" s="81"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -7063,7 +7063,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="84" t="s">
+      <c r="A235" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7089,7 +7089,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="84"/>
+      <c r="A236" s="81"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7425,7 +7425,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A250" s="84" t="s">
+      <c r="A250" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7451,7 +7451,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="84"/>
+      <c r="A251" s="81"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7787,7 +7787,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="84" t="s">
+      <c r="A265" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7813,7 +7813,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="87"/>
+      <c r="A266" s="82"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8123,7 +8123,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A279" s="91" t="s">
+      <c r="A279" s="87" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8149,7 +8149,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A280" s="91"/>
+      <c r="A280" s="87"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8459,7 +8459,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="84" t="s">
+      <c r="A293" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8485,7 +8485,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="87"/>
+      <c r="A294" s="82"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8795,7 +8795,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="89" t="s">
+      <c r="A307" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8821,7 +8821,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A308" s="90"/>
+      <c r="A308" s="86"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9131,7 +9131,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="88" t="s">
+      <c r="A321" s="84" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9157,7 +9157,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A322" s="88"/>
+      <c r="A322" s="84"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9467,7 +9467,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A335" s="84" t="s">
+      <c r="A335" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9493,7 +9493,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A336" s="87"/>
+      <c r="A336" s="82"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9803,7 +9803,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A349" s="84" t="s">
+      <c r="A349" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B349" s="47">
@@ -9829,7 +9829,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A350" s="84"/>
+      <c r="A350" s="81"/>
       <c r="B350" s="48" t="s">
         <v>1</v>
       </c>
@@ -10138,8 +10138,359 @@
         <v>34</v>
       </c>
     </row>
+    <row r="363" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A363" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B363" s="47">
+        <v>46314</v>
+      </c>
+      <c r="C363" s="47">
+        <v>46315</v>
+      </c>
+      <c r="D363" s="47">
+        <v>46316</v>
+      </c>
+      <c r="E363" s="47">
+        <v>46317</v>
+      </c>
+      <c r="F363" s="47">
+        <v>46318</v>
+      </c>
+      <c r="G363" s="47">
+        <v>46319</v>
+      </c>
+      <c r="H363" s="47">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A364" s="81"/>
+      <c r="B364" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C364" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D364" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E364" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F364" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G364" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H364" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A365" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B365" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C365" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="D365" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="E365" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="F365" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G365" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H365" s="78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A366" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B366" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C366" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D366" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F366" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G366" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H366" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A367" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G367" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H367" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A368" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G368" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H368" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A369" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B369" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C369" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D369" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F369" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G369" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="H369" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A370" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B370" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C370" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D370" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E370" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F370" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G370" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H370" s="78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A371" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G371" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="H371" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A372" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G372" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H372" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A373" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B373" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C373" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D373" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E373" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F373" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G373" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H373" s="78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A374" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B374" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C374" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D374" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E374" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F374" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G374" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="H374" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A375" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B375" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C375" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D375" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E375" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F375" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G375" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H375" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
+    <mergeCell ref="A363:A364"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A349:A350"/>
     <mergeCell ref="A335:A336"/>
     <mergeCell ref="A66:A67"/>
@@ -10152,20 +10503,6 @@
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A190:A191"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10185,15 +10522,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -10394,6 +10722,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
@@ -10406,14 +10743,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10430,4 +10759,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{47784282-006C-40E4-A23B-E4A66CEAA64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF97B3E8-BA5D-4963-9AD3-06DA8F327181}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E88081A-A18D-40E2-9336-AE1DB0ADCB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -35,8 +35,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={5ADC6A33-83CB-444B-82B4-1685CD7A1AC8}</author>
+  </authors>
+  <commentList>
+    <comment ref="D382" authorId="0" shapeId="0" xr:uid="{5ADC6A33-83CB-444B-82B4-1685CD7A1AC8}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Media tarde de Cumpleaños</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="48">
   <si>
     <t>GESTOR</t>
   </si>
@@ -178,6 +196,9 @@
   <si>
     <t>31-Aug</t>
   </si>
+  <si>
+    <t>8am - 11:30am</t>
+  </si>
 </sst>
 </file>
 
@@ -186,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +384,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -538,7 +565,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -760,6 +787,12 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -768,6 +801,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -780,18 +825,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -827,7 +860,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>195</xdr:row>
-      <xdr:rowOff>94615</xdr:rowOff>
+      <xdr:rowOff>98425</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -865,6 +898,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Maria Alejandra Sanchez Londoño" id="{E5F1CFC3-A937-4F1C-84C8-6F9906E759A4}" userId="S::maria.sanchez@virtualsoft.tech::2de46a50-02c4-4276-980f-ad46459d3b5a" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1182,9 +1221,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D382" dT="2026-10-22T19:30:24.83" personId="{E5F1CFC3-A937-4F1C-84C8-6F9906E759A4}" id="{5ADC6A33-83CB-444B-82B4-1685CD7A1AC8}">
+    <text>Media tarde de Cumpleaños</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O375"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
+  <dimension ref="A1:O389"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -1197,7 +1244,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1244,7 +1291,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1759,7 +1806,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1785,7 +1832,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2116,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2095,7 +2142,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2379,7 +2426,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2405,7 +2452,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="83"/>
+      <c r="A41" s="85"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2689,7 +2736,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="83" t="s">
+      <c r="A53" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2715,7 +2762,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="83"/>
+      <c r="A54" s="85"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2999,7 +3046,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="83" t="s">
+      <c r="A66" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -3025,7 +3072,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="83"/>
+      <c r="A67" s="85"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3309,7 +3356,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="83" t="s">
+      <c r="A79" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3335,7 +3382,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="83"/>
+      <c r="A80" s="85"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3455,8 +3502,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="90"/>
-      <c r="H84" s="91"/>
+      <c r="G84" s="88"/>
+      <c r="H84" s="89"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3615,7 +3662,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="83" t="s">
+      <c r="A92" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3641,7 +3688,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="83"/>
+      <c r="A93" s="85"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3899,7 +3946,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="83" t="s">
+      <c r="A104" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3925,7 +3972,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="83"/>
+      <c r="A105" s="85"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4183,7 +4230,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="83" t="s">
+      <c r="A116" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4209,7 +4256,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="83"/>
+      <c r="A117" s="85"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4881,7 +4928,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="83" t="s">
+      <c r="A145" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4907,7 +4954,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="83"/>
+      <c r="A146" s="85"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5243,7 +5290,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="83" t="s">
+      <c r="A160" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5269,7 +5316,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="83"/>
+      <c r="A161" s="85"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5605,7 +5652,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="83" t="s">
+      <c r="A175" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5631,7 +5678,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="83"/>
+      <c r="A176" s="85"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5967,7 +6014,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="83" t="s">
+      <c r="A190" s="85" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5993,7 +6040,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="83"/>
+      <c r="A191" s="85"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6329,7 +6376,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="81" t="s">
+      <c r="A205" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6355,7 +6402,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="81"/>
+      <c r="A206" s="83"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6701,7 +6748,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="81" t="s">
+      <c r="A220" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6727,7 +6774,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="81"/>
+      <c r="A221" s="83"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -7063,7 +7110,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="81" t="s">
+      <c r="A235" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7089,7 +7136,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="81"/>
+      <c r="A236" s="83"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7425,7 +7472,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A250" s="81" t="s">
+      <c r="A250" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7451,7 +7498,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="81"/>
+      <c r="A251" s="83"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7787,7 +7834,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="81" t="s">
+      <c r="A265" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7813,7 +7860,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="82"/>
+      <c r="A266" s="84"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8123,7 +8170,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A279" s="87" t="s">
+      <c r="A279" s="93" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8149,7 +8196,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A280" s="87"/>
+      <c r="A280" s="93"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8459,7 +8506,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="81" t="s">
+      <c r="A293" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8485,7 +8532,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="82"/>
+      <c r="A294" s="84"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8795,7 +8842,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="85" t="s">
+      <c r="A307" s="91" t="s">
         <v>0</v>
       </c>
       <c r="B307" s="62">
@@ -8821,7 +8868,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A308" s="86"/>
+      <c r="A308" s="92"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
       </c>
@@ -9131,7 +9178,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="84" t="s">
+      <c r="A321" s="90" t="s">
         <v>0</v>
       </c>
       <c r="B321" s="62">
@@ -9157,7 +9204,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A322" s="84"/>
+      <c r="A322" s="90"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
       </c>
@@ -9467,7 +9514,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A335" s="81" t="s">
+      <c r="A335" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9493,7 +9540,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A336" s="82"/>
+      <c r="A336" s="84"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9803,7 +9850,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A349" s="81" t="s">
+      <c r="A349" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B349" s="47">
@@ -9829,7 +9876,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A350" s="81"/>
+      <c r="A350" s="83"/>
       <c r="B350" s="48" t="s">
         <v>1</v>
       </c>
@@ -10139,7 +10186,7 @@
       </c>
     </row>
     <row r="363" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A363" s="81" t="s">
+      <c r="A363" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B363" s="47">
@@ -10165,7 +10212,7 @@
       </c>
     </row>
     <row r="364" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A364" s="81"/>
+      <c r="A364" s="83"/>
       <c r="B364" s="48" t="s">
         <v>1</v>
       </c>
@@ -10474,9 +10521,344 @@
         <v>10</v>
       </c>
     </row>
+    <row r="377" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A377" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B377" s="47">
+        <v>46321</v>
+      </c>
+      <c r="C377" s="47">
+        <v>46322</v>
+      </c>
+      <c r="D377" s="47">
+        <v>46323</v>
+      </c>
+      <c r="E377" s="47">
+        <v>46324</v>
+      </c>
+      <c r="F377" s="47">
+        <v>46325</v>
+      </c>
+      <c r="G377" s="47">
+        <v>46326</v>
+      </c>
+      <c r="H377" s="47">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A378" s="83"/>
+      <c r="B378" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C378" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D378" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E378" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F378" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G378" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H378" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A379" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G379" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H379" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A380" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B380" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C380" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D380" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="E380" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="F380" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="G380" s="81" t="s">
+        <v>11</v>
+      </c>
+      <c r="H380" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A381" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B381" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C381" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E381" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F381" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G381" s="81" t="s">
+        <v>11</v>
+      </c>
+      <c r="H381" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A382" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B382" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C382" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D382" s="78" t="s">
+        <v>47</v>
+      </c>
+      <c r="E382" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F382" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G382" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H382" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A383" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B383" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C383" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D383" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E383" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F383" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G383" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H383" s="78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A384" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B384" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C384" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D384" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E384" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F384" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G384" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H384" s="78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A385" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B385" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C385" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D385" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E385" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F385" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G385" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H385" s="78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A386" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G386" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H386" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A387" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G387" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H387" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A388" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B388" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C388" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D388" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="E388" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="F388" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G388" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H388" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A389" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B389" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C389" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D389" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E389" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F389" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G389" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H389" s="80" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A363:A364"/>
+  <mergeCells count="28">
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
@@ -10491,22 +10873,25 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="A335:A336"/>
+    <mergeCell ref="A265:A266"/>
+    <mergeCell ref="A377:A378"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A116:A117"/>
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A363:A364"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="A335:A336"/>
     <mergeCell ref="A321:A322"/>
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
-    <mergeCell ref="A265:A266"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Subir a GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E88081A-A18D-40E2-9336-AE1DB0ADCB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8991FA5-59F7-4451-ABF2-8B654F34A4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="48">
   <si>
     <t>GESTOR</t>
   </si>
@@ -207,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,28 +335,33 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -383,12 +388,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -793,14 +792,17 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -808,11 +810,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1231,20 +1230,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O389"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O403"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1290,8 +1289,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="88"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1335,7 +1334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1523,7 +1522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1570,7 +1569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1711,7 +1710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1805,8 +1804,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="86" t="s">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="87" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1831,8 +1830,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="87"/>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="88"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1881,7 +1880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1985,7 +1984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -2115,8 +2114,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="86" t="s">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="87" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -2141,8 +2140,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="88"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2191,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2243,7 +2242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2295,7 +2294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2347,7 +2346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2399,7 +2398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="85" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="85"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -2475,7 +2474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2501,7 +2500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2579,7 +2578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2683,7 +2682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="85" t="s">
         <v>0</v>
       </c>
@@ -2761,7 +2760,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="85"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2785,7 +2784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2811,7 +2810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2863,7 +2862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2941,7 +2940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2967,7 +2966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2993,7 +2992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -3019,7 +3018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -3045,7 +3044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="85" t="s">
         <v>0</v>
       </c>
@@ -3071,7 +3070,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="85"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -3095,7 +3094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -3121,7 +3120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -3147,7 +3146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3199,7 +3198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3251,7 +3250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3277,7 +3276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3303,7 +3302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="85" t="s">
         <v>0</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="85"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -3405,7 +3404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3502,10 +3501,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="88"/>
-      <c r="H84" s="89"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="83"/>
+      <c r="H84" s="84"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3531,7 +3530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3583,7 +3582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3609,7 +3608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3661,7 +3660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="85" t="s">
         <v>0</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="85"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
@@ -3711,7 +3710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3737,7 +3736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3763,7 +3762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3815,7 +3814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3841,7 +3840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3893,7 +3892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3919,7 +3918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="85" t="s">
         <v>0</v>
       </c>
@@ -3971,7 +3970,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="85"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
@@ -3995,7 +3994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -4021,7 +4020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -4047,7 +4046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -4073,7 +4072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -4125,7 +4124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -4151,7 +4150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4203,7 +4202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="85" t="s">
         <v>0</v>
       </c>
@@ -4255,7 +4254,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="85"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
@@ -4279,7 +4278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4331,7 +4330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4357,7 +4356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4383,7 +4382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4409,7 +4408,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4435,7 +4434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4461,7 +4460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4487,7 +4486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4513,7 +4512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4539,7 +4538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4565,7 +4564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4591,7 +4590,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4615,7 +4614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4641,7 +4640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4667,7 +4666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4693,7 +4692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4719,7 +4718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4745,7 +4744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4771,7 +4770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4797,7 +4796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4849,7 +4848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4875,7 +4874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4901,7 +4900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4927,7 +4926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="85" t="s">
         <v>0</v>
       </c>
@@ -4953,7 +4952,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="85"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
@@ -4977,7 +4976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -5003,7 +5002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -5029,7 +5028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -5055,7 +5054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -5081,7 +5080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -5107,7 +5106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -5159,7 +5158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5185,7 +5184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5211,7 +5210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5237,7 +5236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5263,7 +5262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5289,7 +5288,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="85" t="s">
         <v>0</v>
       </c>
@@ -5315,7 +5314,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="85"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
@@ -5339,7 +5338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5391,7 +5390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5417,7 +5416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5443,7 +5442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5469,7 +5468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5495,7 +5494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5521,7 +5520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5547,7 +5546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5573,7 +5572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5651,7 +5650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="85" t="s">
         <v>0</v>
       </c>
@@ -5677,7 +5676,7 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="85"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
@@ -5701,7 +5700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5727,7 +5726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5753,7 +5752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5779,7 +5778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5805,7 +5804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5831,7 +5830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5857,7 +5856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5883,7 +5882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5909,7 +5908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5935,7 +5934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5961,7 +5960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5987,7 +5986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -6013,7 +6012,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="85" t="s">
         <v>0</v>
       </c>
@@ -6039,7 +6038,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="85"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
@@ -6063,7 +6062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -6089,7 +6088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -6115,7 +6114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -6141,7 +6140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -6167,7 +6166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6219,7 +6218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6245,7 +6244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6271,7 +6270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6323,7 +6322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6349,7 +6348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6375,8 +6374,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="83" t="s">
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6401,8 +6400,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="83"/>
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="86"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6425,7 +6424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6451,7 +6450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6477,7 +6476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6529,7 +6528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6555,7 +6554,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6581,7 +6580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6607,7 +6606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6633,7 +6632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6658,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6685,7 +6684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6711,7 +6710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6747,8 +6746,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="83" t="s">
+    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6773,8 +6772,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="83"/>
+    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="86"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6797,7 +6796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6823,7 +6822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6875,7 +6874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6901,7 +6900,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6927,7 +6926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6953,7 +6952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6979,7 +6978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -7005,7 +7004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -7031,7 +7030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -7057,7 +7056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -7083,7 +7082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -7109,8 +7108,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="83" t="s">
+    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -7135,8 +7134,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="83"/>
+    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="86"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7159,7 +7158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7185,7 +7184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7211,7 +7210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7237,7 +7236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7263,7 +7262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7289,7 +7288,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7315,7 +7314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7367,7 +7366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7393,7 +7392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7419,7 +7418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7445,7 +7444,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7471,8 +7470,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A250" s="83" t="s">
+    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7497,8 +7496,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="83"/>
+    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="86"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7521,7 +7520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7547,7 +7546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7599,7 +7598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7625,7 +7624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7651,7 +7650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7677,7 +7676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7703,7 +7702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7729,7 +7728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7755,7 +7754,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7781,7 +7780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7807,7 +7806,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7833,8 +7832,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="83" t="s">
+    <row r="265" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A265" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7859,8 +7858,8 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="84"/>
+    <row r="266" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A266" s="89"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7883,7 +7882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7909,7 +7908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7935,7 +7934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7961,7 +7960,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7987,7 +7986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -8013,7 +8012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -8039,7 +8038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -8065,7 +8064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -8091,7 +8090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -8143,7 +8142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -8169,7 +8168,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="93" t="s">
         <v>0</v>
       </c>
@@ -8195,7 +8194,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="93"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
@@ -8219,7 +8218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8245,7 +8244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8271,7 +8270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8297,7 +8296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8323,7 +8322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8349,7 +8348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8375,7 +8374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8401,7 +8400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8427,7 +8426,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8453,7 +8452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8479,7 +8478,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8505,8 +8504,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="83" t="s">
+    <row r="293" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A293" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8531,8 +8530,8 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="84"/>
+    <row r="294" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A294" s="89"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8555,7 +8554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
@@ -8581,7 +8580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
@@ -8607,7 +8606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
@@ -8659,7 +8658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
@@ -8685,7 +8684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
@@ -8711,7 +8710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
@@ -8737,7 +8736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
@@ -8763,7 +8762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
@@ -8789,7 +8788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
@@ -8815,7 +8814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="91" t="s">
         <v>0</v>
       </c>
@@ -8867,7 +8866,7 @@
         <v>46292</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="92"/>
       <c r="B308" s="63" t="s">
         <v>1</v>
@@ -8891,7 +8890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A309" s="66" t="s">
         <v>17</v>
       </c>
@@ -8917,7 +8916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="66" t="s">
         <v>20</v>
       </c>
@@ -8943,7 +8942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="66" t="s">
         <v>8</v>
       </c>
@@ -8969,7 +8968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="66" t="s">
         <v>23</v>
       </c>
@@ -8995,7 +8994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="66" t="s">
         <v>22</v>
       </c>
@@ -9021,7 +9020,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="66" t="s">
         <v>12</v>
       </c>
@@ -9047,7 +9046,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="66" t="s">
         <v>14</v>
       </c>
@@ -9073,7 +9072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="66" t="s">
         <v>21</v>
       </c>
@@ -9099,7 +9098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="66" t="s">
         <v>18</v>
       </c>
@@ -9125,7 +9124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="69" t="s">
         <v>27</v>
       </c>
@@ -9151,7 +9150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="66" t="s">
         <v>28</v>
       </c>
@@ -9177,7 +9176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="90" t="s">
         <v>0</v>
       </c>
@@ -9203,7 +9202,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="90"/>
       <c r="B322" s="63" t="s">
         <v>1</v>
@@ -9227,7 +9226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A323" s="70" t="s">
         <v>17</v>
       </c>
@@ -9253,7 +9252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="70" t="s">
         <v>21</v>
       </c>
@@ -9279,7 +9278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="70" t="s">
         <v>8</v>
       </c>
@@ -9305,7 +9304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="70" t="s">
         <v>23</v>
       </c>
@@ -9331,7 +9330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="70" t="s">
         <v>22</v>
       </c>
@@ -9357,7 +9356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="70" t="s">
         <v>12</v>
       </c>
@@ -9383,7 +9382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="70" t="s">
         <v>20</v>
       </c>
@@ -9409,7 +9408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="70" t="s">
         <v>14</v>
       </c>
@@ -9435,7 +9434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="70" t="s">
         <v>18</v>
       </c>
@@ -9461,7 +9460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="72" t="s">
         <v>27</v>
       </c>
@@ -9487,7 +9486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="70" t="s">
         <v>28</v>
       </c>
@@ -9513,8 +9512,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A335" s="83" t="s">
+    <row r="335" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A335" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B335" s="47">
@@ -9539,8 +9538,8 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A336" s="84"/>
+    <row r="336" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A336" s="89"/>
       <c r="B336" s="48" t="s">
         <v>1</v>
       </c>
@@ -9563,7 +9562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A337" s="23" t="s">
         <v>17</v>
       </c>
@@ -9589,7 +9588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="23" t="s">
         <v>20</v>
       </c>
@@ -9615,7 +9614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="339" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="23" t="s">
         <v>14</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="23" t="s">
         <v>23</v>
       </c>
@@ -9667,7 +9666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="23" t="s">
         <v>22</v>
       </c>
@@ -9693,7 +9692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="342" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="23" t="s">
         <v>12</v>
       </c>
@@ -9719,7 +9718,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="343" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="23" t="s">
         <v>21</v>
       </c>
@@ -9745,7 +9744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="344" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="23" t="s">
         <v>8</v>
       </c>
@@ -9771,7 +9770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="23" t="s">
         <v>18</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="44" t="s">
         <v>27</v>
       </c>
@@ -9823,7 +9822,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="347" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="23" t="s">
         <v>28</v>
       </c>
@@ -9849,8 +9848,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="349" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A349" s="83" t="s">
+    <row r="349" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A349" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B349" s="47">
@@ -9875,8 +9874,8 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="350" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A350" s="83"/>
+    <row r="350" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A350" s="86"/>
       <c r="B350" s="48" t="s">
         <v>1</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A351" s="23" t="s">
         <v>17</v>
       </c>
@@ -9925,7 +9924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="352" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="23" t="s">
         <v>8</v>
       </c>
@@ -9951,7 +9950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="23" t="s">
         <v>12</v>
       </c>
@@ -9977,7 +9976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="23" t="s">
         <v>23</v>
       </c>
@@ -10003,7 +10002,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="23" t="s">
         <v>22</v>
       </c>
@@ -10029,7 +10028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="23" t="s">
         <v>14</v>
       </c>
@@ -10055,7 +10054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="23" t="s">
         <v>21</v>
       </c>
@@ -10081,7 +10080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="358" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="23" t="s">
         <v>20</v>
       </c>
@@ -10107,7 +10106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="23" t="s">
         <v>18</v>
       </c>
@@ -10133,7 +10132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="44" t="s">
         <v>27</v>
       </c>
@@ -10159,7 +10158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="361" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="23" t="s">
         <v>28</v>
       </c>
@@ -10185,8 +10184,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="363" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A363" s="83" t="s">
+    <row r="363" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A363" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B363" s="47">
@@ -10211,8 +10210,8 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="364" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A364" s="83"/>
+    <row r="364" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A364" s="86"/>
       <c r="B364" s="48" t="s">
         <v>1</v>
       </c>
@@ -10235,7 +10234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="365" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A365" s="23" t="s">
         <v>17</v>
       </c>
@@ -10261,7 +10260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="23" t="s">
         <v>22</v>
       </c>
@@ -10287,7 +10286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="367" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="23" t="s">
         <v>14</v>
       </c>
@@ -10313,7 +10312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="23" t="s">
         <v>21</v>
       </c>
@@ -10339,7 +10338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="23" t="s">
         <v>23</v>
       </c>
@@ -10365,7 +10364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="23" t="s">
         <v>20</v>
       </c>
@@ -10391,7 +10390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="371" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="23" t="s">
         <v>12</v>
       </c>
@@ -10417,7 +10416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="23" t="s">
         <v>8</v>
       </c>
@@ -10443,7 +10442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="23" t="s">
         <v>18</v>
       </c>
@@ -10469,7 +10468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="44" t="s">
         <v>27</v>
       </c>
@@ -10495,7 +10494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="23" t="s">
         <v>28</v>
       </c>
@@ -10521,8 +10520,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A377" s="83" t="s">
+    <row r="377" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A377" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B377" s="47">
@@ -10547,8 +10546,8 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A378" s="83"/>
+    <row r="378" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A378" s="86"/>
       <c r="B378" s="48" t="s">
         <v>1</v>
       </c>
@@ -10571,7 +10570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="23" t="s">
         <v>22</v>
       </c>
@@ -10597,7 +10596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="23" t="s">
         <v>12</v>
       </c>
@@ -10623,7 +10622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="23" t="s">
         <v>20</v>
       </c>
@@ -10649,7 +10648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A382" s="23" t="s">
         <v>23</v>
       </c>
@@ -10675,7 +10674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="383" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="23" t="s">
         <v>8</v>
       </c>
@@ -10701,7 +10700,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="23" t="s">
         <v>14</v>
       </c>
@@ -10727,7 +10726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="23" t="s">
         <v>21</v>
       </c>
@@ -10753,7 +10752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="23" t="s">
         <v>17</v>
       </c>
@@ -10779,7 +10778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="23" t="s">
         <v>18</v>
       </c>
@@ -10805,7 +10804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="44" t="s">
         <v>27</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="23" t="s">
         <v>28</v>
       </c>
@@ -10857,22 +10856,345 @@
         <v>34</v>
       </c>
     </row>
+    <row r="391" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A391" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B391" s="47">
+        <v>46328</v>
+      </c>
+      <c r="C391" s="47">
+        <v>46329</v>
+      </c>
+      <c r="D391" s="47">
+        <v>46330</v>
+      </c>
+      <c r="E391" s="47">
+        <v>46331</v>
+      </c>
+      <c r="F391" s="47">
+        <v>46332</v>
+      </c>
+      <c r="G391" s="47">
+        <v>46333</v>
+      </c>
+      <c r="H391" s="47">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A392" s="86"/>
+      <c r="B392" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C392" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D392" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E392" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F392" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G392" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H392" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A393" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B393" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C393" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D393" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E393" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F393" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G393" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H393" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A394" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B394" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C394" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="D394" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="E394" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="F394" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G394" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H394" s="78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A395" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B395" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C395" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E395" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F395" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G395" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H395" s="78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A396" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G396" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H396" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A397" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B397" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C397" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D397" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E397" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F397" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G397" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="H397" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B398" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C398" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D398" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E398" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F398" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G398" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H398" s="78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A399" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G399" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="H399" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A400" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G400" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H400" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A401" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B401" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C401" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D401" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E401" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F401" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="G401" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H401" s="79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A402" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B402" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C402" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D402" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E402" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F402" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G402" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H402" s="80" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A403" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B403" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C403" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D403" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="E403" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="F403" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G403" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="H403" s="75" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="29">
+    <mergeCell ref="A391:A392"/>
     <mergeCell ref="A265:A266"/>
     <mergeCell ref="A377:A378"/>
     <mergeCell ref="A66:A67"/>
@@ -10887,6 +11209,20 @@
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="A293:A294"/>
     <mergeCell ref="A279:A280"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A190:A191"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10907,6 +11243,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -11107,15 +11452,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
@@ -11128,6 +11464,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11144,12 +11488,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>